--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t>Id</t>
   </si>
@@ -48,7 +48,64 @@
     <t>""</t>
   </si>
   <si>
+    <t>累計1回以上バトルに勝利する</t>
+  </si>
+  <si>
+    <t>いずれかの仲間のキャラLvを2以上にする</t>
+  </si>
+  <si>
+    <t>(Nu)を消費していずれかの仲間のキャラを上げる</t>
+  </si>
+  <si>
+    <t>バトル評価値を5%以上にする</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が100以上なる</t>
+  </si>
+  <si>
+    <t>Rank1の課題を全て達成する</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
+    <t>課題達成</t>
+  </si>
+  <si>
     <t>DepartureCount</t>
+  </si>
+  <si>
+    <t>出撃回数</t>
+  </si>
+  <si>
+    <t>BattleVictory</t>
+  </si>
+  <si>
+    <t>勝利回数</t>
+  </si>
+  <si>
+    <t>CharacterLevel</t>
+  </si>
+  <si>
+    <t>キャラレベル</t>
+  </si>
+  <si>
+    <t>TacticsLvupCount</t>
+  </si>
+  <si>
+    <t>Nu消費レベルアップ回数</t>
+  </si>
+  <si>
+    <t>BattleScore</t>
+  </si>
+  <si>
+    <t>バトル評価値</t>
+  </si>
+  <si>
+    <t>TotalDamage</t>
+  </si>
+  <si>
+    <t>与ダメージ</t>
   </si>
 </sst>
 </file>
@@ -56,9 +113,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -71,95 +128,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -167,9 +135,98 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -193,15 +250,15 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -229,25 +286,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -259,151 +460,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -414,15 +471,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -437,6 +485,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -465,17 +528,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -484,7 +552,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -503,17 +571,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -522,145 +579,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -987,8 +1044,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="9.54545454545454"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -1027,6 +1087,246 @@
         <v>0</v>
       </c>
       <c r="F2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1020</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1020</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>1030</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1030</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>-1</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>1040</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1040</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>1050</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1050</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>1060</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1060</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>1070</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>2010</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>1010</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>2020</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>1020</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>2030</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1030</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>-1</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>2040</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>1040</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>2050</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>1050</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>2060</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>1060</v>
+      </c>
+      <c r="D14">
+        <v>200</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>10</v>
       </c>
     </row>
@@ -1039,11 +1339,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
-    <col min="2" max="2" width="21.4545454545455" customWidth="1"/>
+    <col min="2" max="2" width="35.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1065,6 +1365,72 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1020</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>1030</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>1040</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>1050</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>1060</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>1070</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1077,20 +1443,93 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="1"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="15.6363636363636" customWidth="1"/>
+    <col min="3" max="3" width="9.54545454545454" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3">
       <c r="A2">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
         <v>1010</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>1020</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>1030</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>1040</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>1050</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>1060</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -54,13 +54,13 @@
     <t>いずれかの仲間のキャラLvを2以上にする</t>
   </si>
   <si>
-    <t>(Nu)を消費していずれかの仲間のキャラを上げる</t>
+    <t>(Nu)を消費していずれかの仲間のキャラLvを上げる</t>
   </si>
   <si>
     <t>バトル評価値を5%以上にする</t>
   </si>
   <si>
-    <t>与ダメージ累計が100以上なる</t>
+    <t>与ダメージ累計が100以上になる</t>
   </si>
   <si>
     <t>Rank1の課題を全て達成する</t>
@@ -113,10 +113,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -124,6 +124,27 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -135,16 +156,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -157,39 +171,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,6 +225,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -258,6 +250,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -280,31 +280,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -316,43 +424,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -364,7 +448,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -376,91 +460,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -539,20 +539,20 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -579,145 +579,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
   <si>
     <t>Id</t>
   </si>
@@ -64,6 +64,21 @@
   </si>
   <si>
     <t>Rank1の課題を全て達成する</t>
+  </si>
+  <si>
+    <t>累計3回以上出撃する</t>
+  </si>
+  <si>
+    <t>累計10回以上バトルに勝利する</t>
+  </si>
+  <si>
+    <t>いずれかの仲間のキャラLvを5以上にする</t>
+  </si>
+  <si>
+    <t>バトル評価値を10%以上にする</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が200以上になる</t>
   </si>
   <si>
     <t>Complete</t>
@@ -114,9 +129,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -128,7 +143,59 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -141,8 +208,64 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -156,114 +279,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -280,37 +295,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -322,139 +457,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -489,6 +504,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -507,8 +542,23 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -531,43 +581,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -579,16 +594,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -597,127 +612,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1087,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1241,7 +1256,7 @@
         <v>1020</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1339,8 +1354,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
     <col min="2" max="2" width="35.1818181818182" customWidth="1"/>
@@ -1431,6 +1446,72 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>2010</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>2020</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>2030</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>2040</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>2050</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>2060</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1460,10 +1541,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1471,10 +1552,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1482,10 +1563,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1493,10 +1574,10 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1504,10 +1585,10 @@
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1515,10 +1596,10 @@
         <v>1050</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1526,10 +1607,10 @@
         <v>1060</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="49">
   <si>
     <t>Id</t>
   </si>
@@ -42,19 +42,37 @@
     <t>Help</t>
   </si>
   <si>
+    <t>救済コマンドで仲間を増やす</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>(Nu)を消費していずれかの仲間のキャラLvを上げる</t>
+  </si>
+  <si>
+    <t>編成コマンドで仲間を編成する</t>
+  </si>
+  <si>
+    <t>献上コマンドで魔法を入手する</t>
+  </si>
+  <si>
+    <t>仲間の魔法装備を変更する</t>
+  </si>
+  <si>
+    <t>Rank1の重要課題を全て達成する</t>
+  </si>
+  <si>
     <t>累計1回以上出撃する</t>
   </si>
   <si>
-    <t>""</t>
-  </si>
-  <si>
     <t>累計1回以上バトルに勝利する</t>
   </si>
   <si>
     <t>いずれかの仲間のキャラLvを2以上にする</t>
   </si>
   <si>
-    <t>(Nu)を消費していずれかの仲間のキャラLvを上げる</t>
+    <t>(Nu)を消費していずれかの仲間のキャラLvを2回上げる</t>
   </si>
   <si>
     <t>バトル評価値を5%以上にする</t>
@@ -121,6 +139,30 @@
   </si>
   <si>
     <t>与ダメージ</t>
+  </si>
+  <si>
+    <t>DeckEditCommandCount</t>
+  </si>
+  <si>
+    <t>編成コマンド回数</t>
+  </si>
+  <si>
+    <t>PresentCommandCount</t>
+  </si>
+  <si>
+    <t>献上コマンド回数</t>
+  </si>
+  <si>
+    <t>ReliefCommandCount</t>
+  </si>
+  <si>
+    <t>救済コマンド回数</t>
+  </si>
+  <si>
+    <t>StatusSkillChangeCount</t>
+  </si>
+  <si>
+    <t>魔法編成回数</t>
   </si>
 </sst>
 </file>
@@ -128,10 +170,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -143,14 +185,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -165,23 +215,46 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -194,6 +267,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -201,8 +282,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -216,35 +298,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -257,25 +315,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -295,13 +337,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -313,25 +457,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -343,127 +499,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -486,6 +528,35 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -504,22 +575,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -539,15 +605,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -563,26 +620,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -594,16 +636,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -612,127 +654,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1059,7 +1101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9.54545454545454"/>
@@ -1093,7 +1135,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1010</v>
+        <v>7050</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1102,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>10010</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1113,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1020</v>
+        <v>1040</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1133,16 +1175,16 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1030</v>
+        <v>7020</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1153,7 +1195,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1040</v>
+        <v>7040</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1173,10 +1215,10 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1050</v>
+        <v>7080</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1193,10 +1235,10 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>1060</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1207,13 +1249,13 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>1070</v>
+        <v>2010</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1222,21 +1264,21 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1247,19 +1289,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>2020</v>
+        <v>2030</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -1267,19 +1309,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1287,16 +1329,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1307,16 +1349,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>2050</v>
+        <v>2060</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1327,21 +1369,141 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>2060</v>
+        <v>2070</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14">
-        <v>1060</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>3010</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>1010</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>3020</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>1020</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>3030</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <v>1030</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17">
+        <v>-1</v>
+      </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>3040</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>1040</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>3050</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <v>1050</v>
+      </c>
+      <c r="D19">
+        <v>10</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>3060</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1060</v>
+      </c>
+      <c r="D20">
+        <v>200</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <v>10</v>
       </c>
     </row>
@@ -1354,7 +1516,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
@@ -1440,7 +1602,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>1070</v>
+        <v>2010</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
@@ -1451,7 +1613,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
@@ -1462,7 +1624,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2020</v>
+        <v>2030</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -1473,7 +1635,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
@@ -1484,10 +1646,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
@@ -1495,10 +1657,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>2050</v>
+        <v>2060</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
@@ -1506,12 +1668,78 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>2060</v>
+        <v>2070</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>3010</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>3020</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>3030</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>3040</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>3050</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>3060</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1524,8 +1752,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="15.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="9.54545454545454" customWidth="1"/>
@@ -1541,10 +1769,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1552,10 +1780,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1563,10 +1791,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1574,10 +1802,10 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1585,10 +1813,10 @@
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1596,10 +1824,10 @@
         <v>1050</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1607,10 +1835,54 @@
         <v>1060</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>7020</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>7040</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>7050</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>7080</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -170,10 +170,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -181,13 +181,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -199,10 +192,109 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -216,99 +308,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -343,13 +343,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -361,25 +493,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -391,133 +517,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,26 +535,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -575,17 +555,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -605,6 +579,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -619,15 +628,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -636,145 +636,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="8" spans="1:6">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="48">
   <si>
     <t>Id</t>
   </si>
@@ -66,22 +66,19 @@
     <t>累計1回以上出撃する</t>
   </si>
   <si>
-    <t>累計1回以上バトルに勝利する</t>
-  </si>
-  <si>
-    <t>いずれかの仲間のキャラLvを2以上にする</t>
+    <t>累計5回以上バトルに勝利する</t>
+  </si>
+  <si>
+    <t>いずれかの仲間のキャラLvを3以上にする</t>
   </si>
   <si>
     <t>(Nu)を消費していずれかの仲間のキャラLvを2回上げる</t>
   </si>
   <si>
-    <t>バトル評価値を5%以上にする</t>
-  </si>
-  <si>
-    <t>与ダメージ累計が100以上になる</t>
-  </si>
-  <si>
-    <t>Rank1の課題を全て達成する</t>
+    <t>与ダメージ累計が200を超える</t>
+  </si>
+  <si>
+    <t>Rank2の課題を全て達成する</t>
   </si>
   <si>
     <t>累計3回以上出撃する</t>
@@ -170,8 +167,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -184,6 +181,119 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -193,88 +303,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -290,43 +318,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -337,24 +334,168 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -367,157 +508,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,7 +532,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -555,11 +552,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -575,6 +578,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,33 +621,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,7 +633,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -645,7 +642,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -654,127 +651,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1101,7 +1098,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9.54545454545454"/>
@@ -1278,13 +1275,13 @@
         <v>1020</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>10020</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1298,13 +1295,13 @@
         <v>1030</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10">
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>10030</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1324,7 +1321,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>10040</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1335,16 +1332,16 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>10050</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1355,30 +1352,30 @@
         <v>2</v>
       </c>
       <c r="C13">
-        <v>1060</v>
+        <v>10</v>
       </c>
       <c r="D13">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>2070</v>
+        <v>3010</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1389,16 +1386,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>3010</v>
+        <v>3020</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1409,19 +1406,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>3020</v>
+        <v>3030</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -1429,19 +1426,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>3030</v>
+        <v>3040</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>10</v>
@@ -1449,16 +1446,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>3040</v>
+        <v>3050</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1469,41 +1466,21 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>3050</v>
+        <v>3060</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>3060</v>
-      </c>
-      <c r="B20">
-        <v>3</v>
-      </c>
-      <c r="C20">
-        <v>1060</v>
-      </c>
-      <c r="D20">
-        <v>200</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
         <v>10</v>
       </c>
     </row>
@@ -1516,11 +1493,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
-    <col min="2" max="2" width="35.1818181818182" customWidth="1"/>
+    <col min="2" max="2" width="51.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1668,7 +1645,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>2070</v>
+        <v>3010</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
@@ -1679,7 +1656,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>3010</v>
+        <v>3020</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
@@ -1690,7 +1667,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>3020</v>
+        <v>3030</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
@@ -1701,10 +1678,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>3030</v>
+        <v>3040</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
@@ -1712,10 +1689,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>3040</v>
+        <v>3050</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
         <v>9</v>
@@ -1723,23 +1700,12 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>3050</v>
+        <v>3060</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20">
-        <v>3060</v>
-      </c>
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1769,10 +1735,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
         <v>27</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1780,10 +1746,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
         <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1791,10 +1757,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
         <v>31</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1802,10 +1768,10 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1813,10 +1779,10 @@
         <v>1040</v>
       </c>
       <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
         <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1824,10 +1790,10 @@
         <v>1050</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1835,10 +1801,10 @@
         <v>1060</v>
       </c>
       <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
         <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1846,10 +1812,10 @@
         <v>7020</v>
       </c>
       <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
         <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1857,10 +1823,10 @@
         <v>7040</v>
       </c>
       <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
         <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1868,10 +1834,10 @@
         <v>7050</v>
       </c>
       <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
         <v>45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1879,10 +1845,10 @@
         <v>7080</v>
       </c>
       <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
         <v>47</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
   <si>
     <t>Id</t>
   </si>
@@ -78,6 +78,9 @@
     <t>与ダメージ累計が200を超える</t>
   </si>
   <si>
+    <t>山岳遺跡のボスを撃破する</t>
+  </si>
+  <si>
     <t>Rank2の課題を全て達成する</t>
   </si>
   <si>
@@ -136,6 +139,12 @@
   </si>
   <si>
     <t>与ダメージ</t>
+  </si>
+  <si>
+    <t>ClearStage</t>
+  </si>
+  <si>
+    <t>ステージボスを倒している</t>
   </si>
   <si>
     <t>DeckEditCommandCount</t>
@@ -167,10 +176,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -178,13 +187,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -196,8 +198,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -212,7 +244,69 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,92 +321,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,19 +343,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -358,163 +517,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -552,17 +561,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -582,22 +594,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,8 +626,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -633,145 +642,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1098,7 +1107,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9.54545454545454"/>
@@ -1352,50 +1361,50 @@
         <v>2</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>20010</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>3010</v>
+        <v>2070</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1406,19 +1415,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -1426,19 +1435,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F17">
         <v>10</v>
@@ -1446,16 +1455,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>3050</v>
+        <v>3040</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1466,21 +1475,41 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>3060</v>
+        <v>3050</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="D19">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>3060</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1060</v>
+      </c>
+      <c r="D20">
+        <v>200</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <v>10</v>
       </c>
     </row>
@@ -1493,7 +1522,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
@@ -1645,7 +1674,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>3010</v>
+        <v>2070</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
@@ -1656,7 +1685,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
@@ -1667,7 +1696,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
@@ -1678,10 +1707,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
@@ -1689,10 +1718,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>3050</v>
+        <v>3040</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
         <v>9</v>
@@ -1700,12 +1729,23 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>3060</v>
+        <v>3050</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
       <c r="C19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>3060</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1718,7 +1758,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="15.6363636363636" customWidth="1"/>
@@ -1735,10 +1775,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1746,10 +1786,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1757,10 +1797,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1768,10 +1808,10 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1779,10 +1819,10 @@
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1790,10 +1830,10 @@
         <v>1050</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1801,54 +1841,65 @@
         <v>1060</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>7020</v>
+        <v>2010</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>7040</v>
+        <v>7020</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>7050</v>
+        <v>7040</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
+        <v>7050</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
         <v>7080</v>
       </c>
-      <c r="B12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" t="s">
-        <v>47</v>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -16,11 +16,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="51">
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>Category</t>
+  </si>
+  <si>
     <t>Rank</t>
   </si>
   <si>
@@ -72,7 +75,7 @@
     <t>いずれかの仲間のキャラLvを3以上にする</t>
   </si>
   <si>
-    <t>(Nu)を消費していずれかの仲間のキャラLvを2回上げる</t>
+    <t>バトル評価値を10%以上にする</t>
   </si>
   <si>
     <t>与ダメージ累計が200を超える</t>
@@ -81,7 +84,7 @@
     <t>山岳遺跡のボスを撃破する</t>
   </si>
   <si>
-    <t>Rank2の課題を全て達成する</t>
+    <t>Rank2の重要課題を全て達成する</t>
   </si>
   <si>
     <t>累計3回以上出撃する</t>
@@ -91,9 +94,6 @@
   </si>
   <si>
     <t>いずれかの仲間のキャラLvを5以上にする</t>
-  </si>
-  <si>
-    <t>バトル評価値を10%以上にする</t>
   </si>
   <si>
     <t>与ダメージ累計が200以上になる</t>
@@ -176,10 +176,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -190,8 +190,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -206,30 +242,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,31 +272,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -282,31 +320,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,21 +333,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -343,187 +343,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -534,15 +534,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -557,24 +548,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -594,17 +567,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -626,6 +593,39 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -642,145 +642,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1107,13 +1107,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9.54545454545454"/>
+    <col min="1" max="2" width="9.54545454545454"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1132,384 +1132,444 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1010</v>
       </c>
       <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>7050</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1020</v>
       </c>
       <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1040</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1030</v>
       </c>
       <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
         <v>1</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>7020</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>10010</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1040</v>
       </c>
       <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>7040</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1050</v>
       </c>
       <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>7080</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1060</v>
       </c>
       <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="C7">
-        <v>10</v>
-      </c>
       <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>20010</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>2010</v>
       </c>
       <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8">
         <v>2</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>1010</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>10010</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2020</v>
       </c>
       <c r="B9">
+        <v>10</v>
+      </c>
+      <c r="C9">
         <v>2</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>1020</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>5</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>10020</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2030</v>
       </c>
       <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10">
         <v>2</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>1030</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>3</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>-1</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>10030</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2040</v>
       </c>
       <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
         <v>2</v>
       </c>
-      <c r="C11">
-        <v>1040</v>
-      </c>
       <c r="D11">
-        <v>2</v>
+        <v>1050</v>
       </c>
       <c r="E11">
+        <v>1000</v>
+      </c>
+      <c r="F11">
         <v>0</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>10040</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2050</v>
       </c>
       <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
         <v>2</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>1060</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>200</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>10050</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2060</v>
       </c>
       <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
         <v>2</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>2010</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>21</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2070</v>
       </c>
       <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
         <v>2</v>
       </c>
-      <c r="C14">
-        <v>10</v>
-      </c>
       <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14">
         <v>2</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>20010</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>3010</v>
       </c>
       <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15">
         <v>3</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>1010</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>3</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0</v>
       </c>
-      <c r="F15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>3020</v>
       </c>
       <c r="B16">
+        <v>10</v>
+      </c>
+      <c r="C16">
         <v>3</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>1020</v>
       </c>
-      <c r="D16">
-        <v>10</v>
-      </c>
       <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
         <v>0</v>
       </c>
-      <c r="F16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>3030</v>
       </c>
       <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="C17">
         <v>3</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>1030</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>5</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>-1</v>
       </c>
-      <c r="F17">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>3040</v>
       </c>
       <c r="B18">
+        <v>10</v>
+      </c>
+      <c r="C18">
         <v>3</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>1040</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>3</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0</v>
       </c>
-      <c r="F18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>3050</v>
       </c>
       <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19">
         <v>3</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>1050</v>
       </c>
-      <c r="D19">
-        <v>10</v>
-      </c>
       <c r="E19">
+        <v>10</v>
+      </c>
+      <c r="F19">
         <v>0</v>
       </c>
-      <c r="F19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>3060</v>
       </c>
       <c r="B20">
+        <v>10</v>
+      </c>
+      <c r="C20">
         <v>3</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>1060</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>200</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>10</v>
       </c>
     </row>
@@ -1534,10 +1594,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1545,10 +1605,10 @@
         <v>1010</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1556,10 +1616,10 @@
         <v>1020</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1567,10 +1627,10 @@
         <v>1030</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1578,10 +1638,10 @@
         <v>1040</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1589,10 +1649,10 @@
         <v>1050</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1600,10 +1660,10 @@
         <v>1060</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1611,10 +1671,10 @@
         <v>2010</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1622,10 +1682,10 @@
         <v>2020</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1633,10 +1693,10 @@
         <v>2030</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1644,10 +1704,10 @@
         <v>2040</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1655,10 +1715,10 @@
         <v>2050</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1666,10 +1726,10 @@
         <v>2060</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1677,10 +1737,10 @@
         <v>2070</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1688,10 +1748,10 @@
         <v>3010</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1699,10 +1759,10 @@
         <v>3020</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1710,10 +1770,10 @@
         <v>3030</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1721,10 +1781,10 @@
         <v>3040</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1732,10 +1792,10 @@
         <v>3050</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1746,7 +1806,7 @@
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1767,7 +1827,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
   <si>
     <t>Id</t>
   </si>
@@ -72,7 +72,7 @@
     <t>累計5回以上バトルに勝利する</t>
   </si>
   <si>
-    <t>いずれかの仲間のキャラLvを3以上にする</t>
+    <t>いずれかのキャラLvを3以上にする</t>
   </si>
   <si>
     <t>バトル評価値を10%以上にする</t>
@@ -87,16 +87,19 @@
     <t>Rank2の重要課題を全て達成する</t>
   </si>
   <si>
-    <t>累計3回以上出撃する</t>
-  </si>
-  <si>
-    <t>累計10回以上バトルに勝利する</t>
-  </si>
-  <si>
-    <t>いずれかの仲間のキャラLvを5以上にする</t>
-  </si>
-  <si>
-    <t>与ダメージ累計が200以上になる</t>
+    <t>累計5回以上出撃する</t>
+  </si>
+  <si>
+    <t>累計20回以上バトルに勝利する</t>
+  </si>
+  <si>
+    <t>いずれかのキャラLvを5以上にする</t>
+  </si>
+  <si>
+    <t>バトル評価値を50%以上にする</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が1000以上になる</t>
   </si>
   <si>
     <t>Complete</t>
@@ -176,10 +179,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -190,10 +193,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -204,8 +223,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,25 +246,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,18 +275,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -289,23 +300,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,7 +331,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -343,25 +346,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -373,157 +478,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -534,6 +537,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -595,15 +607,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
@@ -642,145 +645,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1449,13 +1452,13 @@
         <v>1010</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1472,13 +1475,13 @@
         <v>1020</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>10</v>
+        <v>10020</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1501,7 +1504,7 @@
         <v>-1</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>10030</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1515,16 +1518,16 @@
         <v>3</v>
       </c>
       <c r="D18">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>5000</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>10</v>
+        <v>10040</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1538,16 +1541,16 @@
         <v>3</v>
       </c>
       <c r="D19">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>10050</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1561,16 +1564,16 @@
         <v>3</v>
       </c>
       <c r="D20">
-        <v>1060</v>
+        <v>2010</v>
       </c>
       <c r="E20">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1781,7 +1784,7 @@
         <v>3040</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -1792,7 +1795,7 @@
         <v>3050</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -1803,7 +1806,7 @@
         <v>3060</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -1835,10 +1838,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1846,10 +1849,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1857,10 +1860,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1868,10 +1871,10 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1879,10 +1882,10 @@
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1890,10 +1893,10 @@
         <v>1050</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1901,10 +1904,10 @@
         <v>1060</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1912,10 +1915,10 @@
         <v>2010</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1923,10 +1926,10 @@
         <v>7020</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1934,10 +1937,10 @@
         <v>7040</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1945,10 +1948,10 @@
         <v>7050</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1956,10 +1959,10 @@
         <v>7080</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
   <si>
     <t>Id</t>
   </si>
@@ -81,7 +81,7 @@
     <t>与ダメージ累計が200を超える</t>
   </si>
   <si>
-    <t>山岳遺跡のボスを撃破する</t>
+    <t>忘れられた山岳遺跡のボスを撃破する</t>
   </si>
   <si>
     <t>Rank2の重要課題を全て達成する</t>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>与ダメージ累計が1000以上になる</t>
+  </si>
+  <si>
+    <t>月影の森のボスを撃破する</t>
   </si>
   <si>
     <t>Complete</t>
@@ -179,10 +182,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -190,21 +193,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -217,75 +205,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,7 +235,75 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,6 +312,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -346,31 +349,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -382,25 +493,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -412,121 +523,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -537,6 +540,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -588,6 +600,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -598,30 +625,6 @@
         <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -645,145 +648,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1806,7 +1809,7 @@
         <v>3060</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -1838,10 +1841,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1849,10 +1852,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1860,10 +1863,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1871,10 +1874,10 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1882,10 +1885,10 @@
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1893,10 +1896,10 @@
         <v>1050</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1904,10 +1907,10 @@
         <v>1060</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1915,10 +1918,10 @@
         <v>2010</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1926,10 +1929,10 @@
         <v>7020</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1937,10 +1940,10 @@
         <v>7040</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1948,10 +1951,10 @@
         <v>7050</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1959,10 +1962,10 @@
         <v>7080</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -96,7 +96,7 @@
     <t>いずれかのキャラLvを5以上にする</t>
   </si>
   <si>
-    <t>バトル評価値を50%以上にする</t>
+    <t>バトル評価値を30%以上にする</t>
   </si>
   <si>
     <t>与ダメージ累計が1000以上になる</t>
@@ -183,9 +183,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -193,6 +193,21 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -205,6 +220,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -212,7 +242,60 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,21 +310,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -249,32 +317,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,57 +333,12 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -349,187 +349,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,15 +548,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -600,6 +591,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -610,21 +625,6 @@
         <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -648,145 +648,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1524,7 +1524,7 @@
         <v>1050</v>
       </c>
       <c r="E18">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="F18">
         <v>0</v>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="59">
   <si>
     <t>Id</t>
   </si>
@@ -175,6 +175,24 @@
   </si>
   <si>
     <t>魔法編成回数</t>
+  </si>
+  <si>
+    <t>MissionRank</t>
+  </si>
+  <si>
+    <t>ミッションランク値</t>
+  </si>
+  <si>
+    <t>ClearStageNum</t>
+  </si>
+  <si>
+    <t>ステージボスを倒した数</t>
+  </si>
+  <si>
+    <t>PartyEvaluate</t>
+  </si>
+  <si>
+    <t>メンバーの戦力値</t>
   </si>
 </sst>
 </file>
@@ -182,9 +200,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -196,16 +214,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,44 +260,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -272,12 +275,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -285,17 +296,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,17 +312,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,8 +328,31 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -349,13 +367,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -367,169 +547,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,11 +561,28 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,21 +626,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -632,11 +652,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -648,16 +666,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -666,127 +684,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1824,7 +1842,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="15.6363636363636" customWidth="1"/>
@@ -1968,6 +1986,39 @@
         <v>52</v>
       </c>
     </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>8010</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>8020</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>8030</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
   <si>
     <t>Id</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>月影の森のボスを撃破する</t>
+  </si>
+  <si>
+    <t>Rank3の重要課題を全て達成する</t>
   </si>
   <si>
     <t>Complete</t>
@@ -200,10 +203,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -214,49 +217,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -275,7 +239,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -289,10 +253,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -301,14 +265,6 @@
       <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -328,7 +284,22 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -343,20 +314,52 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -367,25 +370,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -397,157 +538,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -558,6 +561,69 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -578,6 +644,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -586,78 +661,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -666,145 +669,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1131,7 +1134,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9.54545454545454"/>
@@ -1427,7 +1430,7 @@
         <v>2010</v>
       </c>
       <c r="E13">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1588,13 +1591,36 @@
         <v>2010</v>
       </c>
       <c r="E20">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
         <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>3070</v>
+      </c>
+      <c r="B21">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>10</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>20010</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +1632,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
@@ -1830,6 +1856,17 @@
         <v>28</v>
       </c>
       <c r="C20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>3070</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1859,10 +1896,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1870,10 +1907,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1881,10 +1918,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1892,10 +1929,10 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1903,10 +1940,10 @@
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1914,10 +1951,10 @@
         <v>1050</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1925,10 +1962,10 @@
         <v>1060</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1936,10 +1973,10 @@
         <v>2010</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1947,10 +1984,10 @@
         <v>7020</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1958,10 +1995,10 @@
         <v>7040</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1969,10 +2006,10 @@
         <v>7050</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1980,10 +2017,10 @@
         <v>7080</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1991,10 +2028,10 @@
         <v>8010</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2002,10 +2039,10 @@
         <v>8020</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2013,10 +2050,10 @@
         <v>8030</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="78">
   <si>
     <t>Id</t>
   </si>
@@ -108,6 +108,36 @@
     <t>Rank3の重要課題を全て達成する</t>
   </si>
   <si>
+    <t>転送コマンドを利用する</t>
+  </si>
+  <si>
+    <t>3人以上のキャラLvを10以上にする</t>
+  </si>
+  <si>
+    <t>戦闘で覚醒スキルを1回以上使用する</t>
+  </si>
+  <si>
+    <t>戦闘で交代を1回以上使用する</t>
+  </si>
+  <si>
+    <t>亡国の宮殿跡地のボスを撃破する</t>
+  </si>
+  <si>
+    <t>累計10回以上出撃する</t>
+  </si>
+  <si>
+    <t>累計40回以上バトルに勝利する</t>
+  </si>
+  <si>
+    <t>いずれかのキャラLvを15以上にする</t>
+  </si>
+  <si>
+    <t>バトル評価値を50%以上にする</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が2500以上になる</t>
+  </si>
+  <si>
     <t>Complete</t>
   </si>
   <si>
@@ -132,6 +162,12 @@
     <t>キャラレベル</t>
   </si>
   <si>
+    <t>CharacterLevelNum</t>
+  </si>
+  <si>
+    <t>キャラレベル人数指定</t>
+  </si>
+  <si>
     <t>TacticsLvupCount</t>
   </si>
   <si>
@@ -156,6 +192,18 @@
     <t>ステージボスを倒している</t>
   </si>
   <si>
+    <t>UseAwakeSkillCount</t>
+  </si>
+  <si>
+    <t>覚醒スキル使用回数</t>
+  </si>
+  <si>
+    <t>UseChangeLineCount</t>
+  </si>
+  <si>
+    <t>交代スキル使用回数</t>
+  </si>
+  <si>
     <t>DeckEditCommandCount</t>
   </si>
   <si>
@@ -172,6 +220,12 @@
   </si>
   <si>
     <t>救済コマンド回数</t>
+  </si>
+  <si>
+    <t>TransferCommandCount</t>
+  </si>
+  <si>
+    <t>転送回数</t>
   </si>
   <si>
     <t>StatusSkillChangeCount</t>
@@ -203,9 +257,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -225,52 +279,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,7 +294,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -298,8 +307,93 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -320,46 +414,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -370,25 +424,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -400,157 +598,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -561,15 +615,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -584,6 +629,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,6 +690,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -626,41 +715,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -669,145 +723,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1134,7 +1188,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9.54545454545454"/>
@@ -1621,6 +1675,236 @@
       </c>
       <c r="G21">
         <v>20010</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>4010</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22">
+        <v>7060</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>40020</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>4020</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23">
+        <v>1031</v>
+      </c>
+      <c r="E23">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23">
+        <v>11010</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>4030</v>
+      </c>
+      <c r="B24">
+        <v>10</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24">
+        <v>3010</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>11020</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>4040</v>
+      </c>
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25">
+        <v>3020</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>11030</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>4050</v>
+      </c>
+      <c r="B26">
+        <v>10</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26">
+        <v>2010</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>4110</v>
+      </c>
+      <c r="B27">
+        <v>20</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27">
+        <v>1010</v>
+      </c>
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>4120</v>
+      </c>
+      <c r="B28">
+        <v>20</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <v>1020</v>
+      </c>
+      <c r="E28">
+        <v>40</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>4130</v>
+      </c>
+      <c r="B29">
+        <v>20</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29">
+        <v>1030</v>
+      </c>
+      <c r="E29">
+        <v>15</v>
+      </c>
+      <c r="F29">
+        <v>-1</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>4140</v>
+      </c>
+      <c r="B30">
+        <v>20</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30">
+        <v>1050</v>
+      </c>
+      <c r="E30">
+        <v>5000</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>4150</v>
+      </c>
+      <c r="B31">
+        <v>20</v>
+      </c>
+      <c r="C31">
+        <v>4</v>
+      </c>
+      <c r="D31">
+        <v>1060</v>
+      </c>
+      <c r="E31">
+        <v>2500</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1632,7 +1916,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
@@ -1867,6 +2151,116 @@
         <v>29</v>
       </c>
       <c r="C21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>4010</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>4020</v>
+      </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>4030</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>4040</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>4050</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>4110</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>4120</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>4130</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>4140</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>4150</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1879,7 +2273,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="15.6363636363636" customWidth="1"/>
@@ -1896,10 +2290,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1907,10 +2301,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1918,10 +2312,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1929,131 +2323,175 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>1040</v>
+        <v>1031</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2010</v>
+        <v>1060</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>7020</v>
+        <v>2010</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>7040</v>
+        <v>3010</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>7050</v>
+        <v>3020</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>7080</v>
+        <v>7020</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>8010</v>
+        <v>7040</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>8020</v>
+        <v>7050</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
+        <v>7060</v>
+      </c>
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>7080</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>8010</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>8020</v>
+      </c>
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
         <v>8030</v>
       </c>
-      <c r="B16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" t="s">
-        <v>59</v>
+      <c r="B20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="79">
   <si>
     <t>Id</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>亡国の宮殿跡地のボスを撃破する</t>
+  </si>
+  <si>
+    <t>Rank4の重要課題を全て達成する</t>
   </si>
   <si>
     <t>累計10回以上出撃する</t>
@@ -257,10 +260,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -278,6 +281,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -285,10 +296,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -301,14 +321,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -323,22 +360,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -352,43 +374,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -400,9 +404,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -424,187 +427,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -615,39 +618,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -662,15 +632,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -692,11 +653,53 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -723,145 +726,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1188,7 +1191,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9.54545454545454"/>
@@ -1794,30 +1797,30 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>4110</v>
+        <v>4060</v>
       </c>
       <c r="B27">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C27">
         <v>4</v>
       </c>
       <c r="D27">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="B28">
         <v>20</v>
@@ -1826,10 +1829,10 @@
         <v>4</v>
       </c>
       <c r="D28">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="E28">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1840,7 +1843,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>4130</v>
+        <v>4120</v>
       </c>
       <c r="B29">
         <v>20</v>
@@ -1849,13 +1852,13 @@
         <v>4</v>
       </c>
       <c r="D29">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -1863,7 +1866,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="B30">
         <v>20</v>
@@ -1872,13 +1875,13 @@
         <v>4</v>
       </c>
       <c r="D30">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="E30">
-        <v>5000</v>
+        <v>15</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -1886,7 +1889,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>4150</v>
+        <v>4140</v>
       </c>
       <c r="B31">
         <v>20</v>
@@ -1895,15 +1898,38 @@
         <v>4</v>
       </c>
       <c r="D31">
+        <v>1050</v>
+      </c>
+      <c r="E31">
+        <v>5000</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>4150</v>
+      </c>
+      <c r="B32">
+        <v>20</v>
+      </c>
+      <c r="C32">
+        <v>4</v>
+      </c>
+      <c r="D32">
         <v>1060</v>
       </c>
-      <c r="E31">
+      <c r="E32">
         <v>2500</v>
       </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31">
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
         <v>5</v>
       </c>
     </row>
@@ -1916,7 +1942,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
@@ -2211,7 +2237,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>4110</v>
+        <v>4060</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
@@ -2222,7 +2248,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="B28" t="s">
         <v>36</v>
@@ -2233,7 +2259,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>4130</v>
+        <v>4120</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -2244,7 +2270,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="B30" t="s">
         <v>38</v>
@@ -2255,12 +2281,23 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>4150</v>
+        <v>4140</v>
       </c>
       <c r="B31" t="s">
         <v>39</v>
       </c>
       <c r="C31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>4150</v>
+      </c>
+      <c r="B32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2290,10 +2327,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2301,10 +2338,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2312,10 +2349,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2323,10 +2360,10 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2334,10 +2371,10 @@
         <v>1031</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2345,10 +2382,10 @@
         <v>1040</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2356,10 +2393,10 @@
         <v>1050</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2367,10 +2404,10 @@
         <v>1060</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2378,10 +2415,10 @@
         <v>2010</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2389,10 +2426,10 @@
         <v>3010</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2400,10 +2437,10 @@
         <v>3020</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2411,10 +2448,10 @@
         <v>7020</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2422,10 +2459,10 @@
         <v>7040</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2433,10 +2470,10 @@
         <v>7050</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2444,10 +2481,10 @@
         <v>7060</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2455,10 +2492,10 @@
         <v>7080</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2466,10 +2503,10 @@
         <v>8010</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2477,10 +2514,10 @@
         <v>8020</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2488,10 +2525,10 @@
         <v>8030</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -111,6 +111,27 @@
     <t>転送コマンドを利用する</t>
   </si>
   <si>
+    <t>亡国の宮殿跡地のボスを撃破する</t>
+  </si>
+  <si>
+    <t>Rank4の重要課題を全て達成する</t>
+  </si>
+  <si>
+    <t>累計10回以上出撃する</t>
+  </si>
+  <si>
+    <t>累計40回以上バトルに勝利する</t>
+  </si>
+  <si>
+    <t>いずれかのキャラLvを15以上にする</t>
+  </si>
+  <si>
+    <t>バトル評価値を50%以上にする</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が2500以上になる</t>
+  </si>
+  <si>
     <t>3人以上のキャラLvを10以上にする</t>
   </si>
   <si>
@@ -118,27 +139,6 @@
   </si>
   <si>
     <t>戦闘で交代を1回以上使用する</t>
-  </si>
-  <si>
-    <t>亡国の宮殿跡地のボスを撃破する</t>
-  </si>
-  <si>
-    <t>Rank4の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>累計10回以上出撃する</t>
-  </si>
-  <si>
-    <t>累計40回以上バトルに勝利する</t>
-  </si>
-  <si>
-    <t>いずれかのキャラLvを15以上にする</t>
-  </si>
-  <si>
-    <t>バトル評価値を50%以上にする</t>
-  </si>
-  <si>
-    <t>与ダメージ累計が2500以上になる</t>
   </si>
   <si>
     <t>Complete</t>
@@ -262,28 +262,13 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -296,19 +281,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -320,10 +296,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -343,6 +335,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -352,7 +351,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,18 +373,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -396,14 +388,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -411,8 +395,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -427,187 +427,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -622,15 +622,59 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -651,46 +695,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -703,21 +718,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -726,16 +726,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -747,124 +747,124 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1714,16 +1714,16 @@
         <v>4</v>
       </c>
       <c r="D23">
-        <v>1031</v>
+        <v>2010</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>11010</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1737,90 +1737,90 @@
         <v>4</v>
       </c>
       <c r="D24">
-        <v>3010</v>
+        <v>10</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>11020</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>4040</v>
+        <v>4110</v>
       </c>
       <c r="B25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C25">
         <v>4</v>
       </c>
       <c r="D25">
-        <v>3020</v>
+        <v>1010</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>11030</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>4050</v>
+        <v>4120</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C26">
         <v>4</v>
       </c>
       <c r="D26">
-        <v>2010</v>
+        <v>1020</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>4060</v>
+        <v>4130</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C27">
         <v>4</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>1030</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G27">
-        <v>20010</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>4110</v>
+        <v>4140</v>
       </c>
       <c r="B28">
         <v>20</v>
@@ -1829,10 +1829,10 @@
         <v>4</v>
       </c>
       <c r="D28">
-        <v>1010</v>
+        <v>1050</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>5000</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>4120</v>
+        <v>4150</v>
       </c>
       <c r="B29">
         <v>20</v>
@@ -1852,10 +1852,10 @@
         <v>4</v>
       </c>
       <c r="D29">
-        <v>1020</v>
+        <v>1060</v>
       </c>
       <c r="E29">
-        <v>40</v>
+        <v>2500</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1866,71 +1866,71 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>4130</v>
+        <v>5010</v>
       </c>
       <c r="B30">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>11010</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>4140</v>
+        <v>5020</v>
       </c>
       <c r="B31">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31">
-        <v>1050</v>
+        <v>3010</v>
       </c>
       <c r="E31">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>11020</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>4150</v>
+        <v>5030</v>
       </c>
       <c r="B32">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D32">
-        <v>1060</v>
+        <v>3020</v>
       </c>
       <c r="E32">
-        <v>2500</v>
+        <v>1</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>11030</v>
       </c>
     </row>
   </sheetData>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>4040</v>
+        <v>4110</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>4050</v>
+        <v>4120</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>4060</v>
+        <v>4130</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
@@ -2248,7 +2248,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>4110</v>
+        <v>4140</v>
       </c>
       <c r="B28" t="s">
         <v>36</v>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>4120</v>
+        <v>4150</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>4130</v>
+        <v>5010</v>
       </c>
       <c r="B30" t="s">
         <v>38</v>
@@ -2281,7 +2281,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>4140</v>
+        <v>5020</v>
       </c>
       <c r="B31" t="s">
         <v>39</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>4150</v>
+        <v>5030</v>
       </c>
       <c r="B32" t="s">
         <v>40</v>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -260,10 +260,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -274,6 +274,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -281,23 +304,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -311,15 +319,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -335,8 +334,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -351,7 +351,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -360,6 +360,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,30 +381,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -411,8 +396,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -427,187 +427,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -618,6 +618,35 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -636,45 +665,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -695,16 +695,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -713,8 +713,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -726,145 +726,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1723,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:7">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="87">
   <si>
     <t>Id</t>
   </si>
@@ -111,34 +111,58 @@
     <t>転送コマンドを利用する</t>
   </si>
   <si>
+    <t>Rank4の重要課題を全て達成する</t>
+  </si>
+  <si>
+    <t>累計10回以上出撃する</t>
+  </si>
+  <si>
+    <t>累計40回以上バトルに勝利する</t>
+  </si>
+  <si>
+    <t>いずれかのキャラLvを15以上にする</t>
+  </si>
+  <si>
+    <t>バトル評価値を50%以上にする</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が2500以上になる</t>
+  </si>
+  <si>
+    <t>3人以上のキャラLvを10以上にする</t>
+  </si>
+  <si>
+    <t>戦闘で覚醒スキルを1回以上使用する</t>
+  </si>
+  <si>
+    <t>戦闘で交代を1回以上使用する</t>
+  </si>
+  <si>
     <t>亡国の宮殿跡地のボスを撃破する</t>
   </si>
   <si>
-    <t>Rank4の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>累計10回以上出撃する</t>
-  </si>
-  <si>
-    <t>累計40回以上バトルに勝利する</t>
-  </si>
-  <si>
-    <t>いずれかのキャラLvを15以上にする</t>
-  </si>
-  <si>
-    <t>バトル評価値を50%以上にする</t>
-  </si>
-  <si>
-    <t>与ダメージ累計が2500以上になる</t>
-  </si>
-  <si>
-    <t>3人以上のキャラLvを10以上にする</t>
-  </si>
-  <si>
-    <t>戦闘で覚醒スキルを1回以上使用する</t>
-  </si>
-  <si>
-    <t>戦闘で交代を1回以上使用する</t>
+    <t>Rank5の重要課題を全て達成する</t>
+  </si>
+  <si>
+    <t>累計15回以上出撃する</t>
+  </si>
+  <si>
+    <t>累計80回以上バトルに勝利する</t>
+  </si>
+  <si>
+    <t>いずれかのキャラLvを25以上にする</t>
+  </si>
+  <si>
+    <t>バトル評価値を100%以上にする</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が5000以上になる</t>
+  </si>
+  <si>
+    <t>暗黒の塔のボスを撃破する</t>
+  </si>
+  <si>
+    <t>Rank6の重要課題を全て達成する</t>
   </si>
   <si>
     <t>Complete</t>
@@ -261,9 +285,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -271,6 +295,42 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -283,24 +343,40 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -313,14 +389,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -336,22 +428,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -359,60 +436,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -427,25 +451,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -457,25 +553,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -487,13 +571,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -505,109 +619,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -618,6 +642,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -639,28 +678,26 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -676,21 +713,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -712,9 +734,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -726,7 +750,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -735,7 +759,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -744,127 +768,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1191,7 +1215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9.54545454545454"/>
@@ -1240,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1263,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1309,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1332,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1714,44 +1738,44 @@
         <v>4</v>
       </c>
       <c r="D23">
-        <v>2010</v>
+        <v>10</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>20</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>4030</v>
+        <v>4110</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C24">
         <v>4</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>20010</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>4110</v>
+        <v>4120</v>
       </c>
       <c r="B25">
         <v>20</v>
@@ -1760,10 +1784,10 @@
         <v>4</v>
       </c>
       <c r="D25">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1774,7 +1798,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>4120</v>
+        <v>4130</v>
       </c>
       <c r="B26">
         <v>20</v>
@@ -1783,13 +1807,13 @@
         <v>4</v>
       </c>
       <c r="D26">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="E26">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -1797,7 +1821,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>4130</v>
+        <v>4140</v>
       </c>
       <c r="B27">
         <v>20</v>
@@ -1806,13 +1830,13 @@
         <v>4</v>
       </c>
       <c r="D27">
-        <v>1030</v>
+        <v>1050</v>
       </c>
       <c r="E27">
-        <v>15</v>
+        <v>5000</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -1820,7 +1844,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>4140</v>
+        <v>4150</v>
       </c>
       <c r="B28">
         <v>20</v>
@@ -1829,10 +1853,10 @@
         <v>4</v>
       </c>
       <c r="D28">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="E28">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1843,30 +1867,30 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>4150</v>
+        <v>5010</v>
       </c>
       <c r="B29">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29">
-        <v>1060</v>
+        <v>1031</v>
       </c>
       <c r="E29">
-        <v>2500</v>
+        <v>10</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>11010</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>5010</v>
+        <v>5020</v>
       </c>
       <c r="B30">
         <v>10</v>
@@ -1875,21 +1899,21 @@
         <v>5</v>
       </c>
       <c r="D30">
-        <v>1031</v>
+        <v>3010</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>11010</v>
+        <v>11020</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>5020</v>
+        <v>5030</v>
       </c>
       <c r="B31">
         <v>10</v>
@@ -1898,7 +1922,7 @@
         <v>5</v>
       </c>
       <c r="D31">
-        <v>3010</v>
+        <v>3020</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -1907,12 +1931,12 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>11020</v>
+        <v>11030</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>5030</v>
+        <v>5040</v>
       </c>
       <c r="B32">
         <v>10</v>
@@ -1921,16 +1945,200 @@
         <v>5</v>
       </c>
       <c r="D32">
-        <v>3020</v>
+        <v>2010</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>11030</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>5050</v>
+      </c>
+      <c r="B33">
+        <v>10</v>
+      </c>
+      <c r="C33">
+        <v>5</v>
+      </c>
+      <c r="D33">
+        <v>10</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>20010</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>5110</v>
+      </c>
+      <c r="B34">
+        <v>20</v>
+      </c>
+      <c r="C34">
+        <v>5</v>
+      </c>
+      <c r="D34">
+        <v>1010</v>
+      </c>
+      <c r="E34">
+        <v>15</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>5120</v>
+      </c>
+      <c r="B35">
+        <v>20</v>
+      </c>
+      <c r="C35">
+        <v>5</v>
+      </c>
+      <c r="D35">
+        <v>1020</v>
+      </c>
+      <c r="E35">
+        <v>80</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>5130</v>
+      </c>
+      <c r="B36">
+        <v>20</v>
+      </c>
+      <c r="C36">
+        <v>5</v>
+      </c>
+      <c r="D36">
+        <v>1030</v>
+      </c>
+      <c r="E36">
+        <v>25</v>
+      </c>
+      <c r="F36">
+        <v>-1</v>
+      </c>
+      <c r="G36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>5140</v>
+      </c>
+      <c r="B37">
+        <v>20</v>
+      </c>
+      <c r="C37">
+        <v>5</v>
+      </c>
+      <c r="D37">
+        <v>1050</v>
+      </c>
+      <c r="E37">
+        <v>10000</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>5150</v>
+      </c>
+      <c r="B38">
+        <v>20</v>
+      </c>
+      <c r="C38">
+        <v>5</v>
+      </c>
+      <c r="D38">
+        <v>1060</v>
+      </c>
+      <c r="E38">
+        <v>5000</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>6040</v>
+      </c>
+      <c r="B39">
+        <v>10</v>
+      </c>
+      <c r="C39">
+        <v>6</v>
+      </c>
+      <c r="D39">
+        <v>2010</v>
+      </c>
+      <c r="E39">
+        <v>5</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>6050</v>
+      </c>
+      <c r="B40">
+        <v>10</v>
+      </c>
+      <c r="C40">
+        <v>6</v>
+      </c>
+      <c r="D40">
+        <v>10</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>20010</v>
       </c>
     </row>
   </sheetData>
@@ -1942,7 +2150,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
@@ -2204,7 +2412,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>4030</v>
+        <v>4110</v>
       </c>
       <c r="B24" t="s">
         <v>32</v>
@@ -2215,7 +2423,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>4110</v>
+        <v>4120</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
@@ -2226,7 +2434,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>4120</v>
+        <v>4130</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -2237,7 +2445,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>4130</v>
+        <v>4140</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
@@ -2248,7 +2456,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>4140</v>
+        <v>4150</v>
       </c>
       <c r="B28" t="s">
         <v>36</v>
@@ -2259,7 +2467,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>4150</v>
+        <v>5010</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -2270,7 +2478,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>5010</v>
+        <v>5020</v>
       </c>
       <c r="B30" t="s">
         <v>38</v>
@@ -2281,7 +2489,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>5020</v>
+        <v>5030</v>
       </c>
       <c r="B31" t="s">
         <v>39</v>
@@ -2292,12 +2500,100 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>5030</v>
+        <v>5040</v>
       </c>
       <c r="B32" t="s">
         <v>40</v>
       </c>
       <c r="C32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>5050</v>
+      </c>
+      <c r="B33" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>5110</v>
+      </c>
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>5120</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>5130</v>
+      </c>
+      <c r="B36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>5140</v>
+      </c>
+      <c r="B37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>5150</v>
+      </c>
+      <c r="B38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>6040</v>
+      </c>
+      <c r="B39" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>6050</v>
+      </c>
+      <c r="B40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2327,10 +2623,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2338,10 +2634,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2349,10 +2645,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2360,10 +2656,10 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2371,10 +2667,10 @@
         <v>1031</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2382,10 +2678,10 @@
         <v>1040</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2393,10 +2689,10 @@
         <v>1050</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2404,10 +2700,10 @@
         <v>1060</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2415,10 +2711,10 @@
         <v>2010</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2426,10 +2722,10 @@
         <v>3010</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2437,10 +2733,10 @@
         <v>3020</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2448,10 +2744,10 @@
         <v>7020</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2459,10 +2755,10 @@
         <v>7040</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2470,10 +2766,10 @@
         <v>7050</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2481,10 +2777,10 @@
         <v>7060</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2492,10 +2788,10 @@
         <v>7080</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2503,10 +2799,10 @@
         <v>8010</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2514,10 +2810,10 @@
         <v>8020</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2525,10 +2821,10 @@
         <v>8030</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -45,7 +45,7 @@
     <t>Help</t>
   </si>
   <si>
-    <t>救済コマンドで仲間を増やす</t>
+    <t>招聘コマンドで仲間を増やす</t>
   </si>
   <si>
     <t>""</t>
@@ -284,10 +284,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -299,7 +299,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -313,22 +320,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,15 +334,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -372,19 +358,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -402,9 +379,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -436,11 +428,19 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -451,187 +451,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -669,15 +669,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -696,8 +687,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -734,11 +736,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -750,145 +750,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="86">
   <si>
     <t>Id</t>
   </si>
@@ -75,31 +75,31 @@
     <t>いずれかのキャラLvを3以上にする</t>
   </si>
   <si>
+    <t>バトル評価値を5%以上にする</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が200を超える</t>
+  </si>
+  <si>
+    <t>忘れられた山岳遺跡のボスを撃破する</t>
+  </si>
+  <si>
+    <t>Rank2の重要課題を全て達成する</t>
+  </si>
+  <si>
+    <t>累計5回以上出撃する</t>
+  </si>
+  <si>
+    <t>累計30回以上バトルに勝利する</t>
+  </si>
+  <si>
+    <t>いずれかのキャラLvを7以上にする</t>
+  </si>
+  <si>
     <t>バトル評価値を10%以上にする</t>
   </si>
   <si>
-    <t>与ダメージ累計が200を超える</t>
-  </si>
-  <si>
-    <t>忘れられた山岳遺跡のボスを撃破する</t>
-  </si>
-  <si>
-    <t>Rank2の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>累計5回以上出撃する</t>
-  </si>
-  <si>
-    <t>累計20回以上バトルに勝利する</t>
-  </si>
-  <si>
-    <t>いずれかのキャラLvを5以上にする</t>
-  </si>
-  <si>
-    <t>バトル評価値を30%以上にする</t>
-  </si>
-  <si>
-    <t>与ダメージ累計が1000以上になる</t>
+    <t>与ダメージ累計が1500以上になる</t>
   </si>
   <si>
     <t>月影の森のボスを撃破する</t>
@@ -123,10 +123,10 @@
     <t>いずれかのキャラLvを15以上にする</t>
   </si>
   <si>
-    <t>バトル評価値を50%以上にする</t>
-  </si>
-  <si>
-    <t>与ダメージ累計が2500以上になる</t>
+    <t>バトル評価値を25%以上にする</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が5000以上になる</t>
   </si>
   <si>
     <t>3人以上のキャラLvを10以上にする</t>
@@ -153,10 +153,7 @@
     <t>いずれかのキャラLvを25以上にする</t>
   </si>
   <si>
-    <t>バトル評価値を100%以上にする</t>
-  </si>
-  <si>
-    <t>与ダメージ累計が5000以上になる</t>
+    <t>バトル評価値を20%以上にする</t>
   </si>
   <si>
     <t>暗黒の塔のボスを撃破する</t>
@@ -285,9 +282,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -299,7 +296,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -312,8 +309,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -327,24 +332,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -358,10 +347,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -379,6 +385,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -386,11 +393,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -411,36 +425,19 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -451,19 +448,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -475,61 +604,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -541,97 +622,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -656,6 +653,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -686,15 +716,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -718,30 +739,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -750,145 +747,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1465,7 +1462,7 @@
         <v>1050</v>
       </c>
       <c r="E11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1580,7 +1577,7 @@
         <v>1020</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1603,7 +1600,7 @@
         <v>1030</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -1626,7 +1623,7 @@
         <v>1050</v>
       </c>
       <c r="E18">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1649,7 +1646,7 @@
         <v>1060</v>
       </c>
       <c r="E19">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1833,7 +1830,7 @@
         <v>1050</v>
       </c>
       <c r="E27">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1856,7 +1853,7 @@
         <v>1060</v>
       </c>
       <c r="E28">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -2063,7 +2060,7 @@
         <v>1050</v>
       </c>
       <c r="E37">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2569,7 +2566,7 @@
         <v>5150</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C38" t="s">
         <v>10</v>
@@ -2580,7 +2577,7 @@
         <v>6040</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" t="s">
         <v>10</v>
@@ -2591,7 +2588,7 @@
         <v>6050</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
         <v>10</v>
@@ -2623,10 +2620,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2634,10 +2631,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
         <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2645,10 +2642,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
         <v>53</v>
-      </c>
-      <c r="C4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2656,10 +2653,10 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
         <v>55</v>
-      </c>
-      <c r="C5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2667,10 +2664,10 @@
         <v>1031</v>
       </c>
       <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
         <v>57</v>
-      </c>
-      <c r="C6" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2678,10 +2675,10 @@
         <v>1040</v>
       </c>
       <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s">
         <v>59</v>
-      </c>
-      <c r="C7" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2689,10 +2686,10 @@
         <v>1050</v>
       </c>
       <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s">
         <v>61</v>
-      </c>
-      <c r="C8" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2700,10 +2697,10 @@
         <v>1060</v>
       </c>
       <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
         <v>63</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2711,10 +2708,10 @@
         <v>2010</v>
       </c>
       <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
         <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2722,10 +2719,10 @@
         <v>3010</v>
       </c>
       <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
         <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2733,10 +2730,10 @@
         <v>3020</v>
       </c>
       <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
         <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2744,10 +2741,10 @@
         <v>7020</v>
       </c>
       <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
         <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2755,10 +2752,10 @@
         <v>7040</v>
       </c>
       <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
         <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2766,10 +2763,10 @@
         <v>7050</v>
       </c>
       <c r="B15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" t="s">
         <v>75</v>
-      </c>
-      <c r="C15" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2777,10 +2774,10 @@
         <v>7060</v>
       </c>
       <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" t="s">
         <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2788,10 +2785,10 @@
         <v>7080</v>
       </c>
       <c r="B17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" t="s">
         <v>79</v>
-      </c>
-      <c r="C17" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2799,10 +2796,10 @@
         <v>8010</v>
       </c>
       <c r="B18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" t="s">
         <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2810,10 +2807,10 @@
         <v>8020</v>
       </c>
       <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
         <v>83</v>
-      </c>
-      <c r="C19" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2821,10 +2818,10 @@
         <v>8030</v>
       </c>
       <c r="B20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" t="s">
         <v>85</v>
-      </c>
-      <c r="C20" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="87">
   <si>
     <t>Id</t>
   </si>
@@ -123,37 +123,40 @@
     <t>いずれかのキャラLvを15以上にする</t>
   </si>
   <si>
+    <t>バトル評価値を20%以上にする</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が5000以上になる</t>
+  </si>
+  <si>
+    <t>3人以上のキャラLvを20以上にする</t>
+  </si>
+  <si>
+    <t>戦闘で覚醒スキルを1回以上使用する</t>
+  </si>
+  <si>
+    <t>戦闘で交代を1回以上使用する</t>
+  </si>
+  <si>
+    <t>亡国の宮殿跡地のボスを撃破する</t>
+  </si>
+  <si>
+    <t>Rank5の重要課題を全て達成する</t>
+  </si>
+  <si>
+    <t>累計15回以上出撃する</t>
+  </si>
+  <si>
+    <t>累計80回以上バトルに勝利する</t>
+  </si>
+  <si>
+    <t>いずれかのキャラLvを25以上にする</t>
+  </si>
+  <si>
     <t>バトル評価値を25%以上にする</t>
   </si>
   <si>
-    <t>与ダメージ累計が5000以上になる</t>
-  </si>
-  <si>
-    <t>3人以上のキャラLvを10以上にする</t>
-  </si>
-  <si>
-    <t>戦闘で覚醒スキルを1回以上使用する</t>
-  </si>
-  <si>
-    <t>戦闘で交代を1回以上使用する</t>
-  </si>
-  <si>
-    <t>亡国の宮殿跡地のボスを撃破する</t>
-  </si>
-  <si>
-    <t>Rank5の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>累計15回以上出撃する</t>
-  </si>
-  <si>
-    <t>累計80回以上バトルに勝利する</t>
-  </si>
-  <si>
-    <t>いずれかのキャラLvを25以上にする</t>
-  </si>
-  <si>
-    <t>バトル評価値を20%以上にする</t>
+    <t>与ダメージ累計が7500以上になる</t>
   </si>
   <si>
     <t>暗黒の塔のボスを撃破する</t>
@@ -282,8 +285,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
@@ -296,36 +299,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,9 +320,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -355,19 +358,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -386,45 +412,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -433,7 +420,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -448,187 +451,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -639,30 +642,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -685,7 +664,37 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -694,7 +703,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -725,17 +734,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -747,145 +750,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1830,7 +1833,7 @@
         <v>1050</v>
       </c>
       <c r="E27">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1876,7 +1879,7 @@
         <v>1031</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F29">
         <v>3</v>
@@ -2060,7 +2063,7 @@
         <v>1050</v>
       </c>
       <c r="E37">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2083,7 +2086,7 @@
         <v>1060</v>
       </c>
       <c r="E38">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2566,7 +2569,7 @@
         <v>5150</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C38" t="s">
         <v>10</v>
@@ -2577,7 +2580,7 @@
         <v>6040</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
         <v>10</v>
@@ -2588,7 +2591,7 @@
         <v>6050</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C40" t="s">
         <v>10</v>
@@ -2620,10 +2623,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2631,10 +2634,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2642,10 +2645,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2653,10 +2656,10 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2664,10 +2667,10 @@
         <v>1031</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2675,10 +2678,10 @@
         <v>1040</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2686,10 +2689,10 @@
         <v>1050</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2697,10 +2700,10 @@
         <v>1060</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2708,10 +2711,10 @@
         <v>2010</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2719,10 +2722,10 @@
         <v>3010</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2730,10 +2733,10 @@
         <v>3020</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2741,10 +2744,10 @@
         <v>7020</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2752,10 +2755,10 @@
         <v>7040</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2763,10 +2766,10 @@
         <v>7050</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2774,10 +2777,10 @@
         <v>7060</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2785,10 +2788,10 @@
         <v>7080</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2796,10 +2799,10 @@
         <v>8010</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2807,10 +2810,10 @@
         <v>8020</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2818,10 +2821,10 @@
         <v>8030</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="91">
   <si>
     <t>Id</t>
   </si>
@@ -108,10 +108,16 @@
     <t>Rank3の重要課題を全て達成する</t>
   </si>
   <si>
+    <t>戦争(BattleField)ステージに出撃する</t>
+  </si>
+  <si>
+    <t>Rank4の重要課題を全て達成する</t>
+  </si>
+  <si>
     <t>転送コマンドを利用する</t>
   </si>
   <si>
-    <t>Rank4の重要課題を全て達成する</t>
+    <t>Rank5の重要課題を全て達成する</t>
   </si>
   <si>
     <t>累計10回以上出撃する</t>
@@ -129,7 +135,7 @@
     <t>与ダメージ累計が5000以上になる</t>
   </si>
   <si>
-    <t>3人以上のキャラLvを20以上にする</t>
+    <t>3人以上のキャラLvを15以上にする</t>
   </si>
   <si>
     <t>戦闘で覚醒スキルを1回以上使用する</t>
@@ -141,7 +147,7 @@
     <t>亡国の宮殿跡地のボスを撃破する</t>
   </si>
   <si>
-    <t>Rank5の重要課題を全て達成する</t>
+    <t>Rank6の重要課題を全て達成する</t>
   </si>
   <si>
     <t>累計15回以上出撃する</t>
@@ -162,7 +168,7 @@
     <t>暗黒の塔のボスを撃破する</t>
   </si>
   <si>
-    <t>Rank6の重要課題を全て達成する</t>
+    <t>Rank7の重要課題を全て達成する</t>
   </si>
   <si>
     <t>Complete</t>
@@ -175,6 +181,12 @@
   </si>
   <si>
     <t>出撃回数</t>
+  </si>
+  <si>
+    <t>DepartureBattleFieldCount</t>
+  </si>
+  <si>
+    <t>戦争出撃回数</t>
   </si>
   <si>
     <t>BattleVictory</t>
@@ -286,8 +298,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -299,37 +311,74 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -343,6 +392,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -358,25 +424,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -391,52 +441,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -451,6 +463,174 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -463,175 +643,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -642,30 +654,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -680,6 +668,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -703,22 +715,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -737,8 +734,23 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -750,7 +762,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -759,7 +771,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -768,127 +780,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1215,7 +1227,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9.54545454545454"/>
@@ -1715,7 +1727,7 @@
         <v>4</v>
       </c>
       <c r="D22">
-        <v>7060</v>
+        <v>1012</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1724,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>40020</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1752,68 +1764,68 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>4110</v>
+        <v>5010</v>
       </c>
       <c r="B24">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>1010</v>
+        <v>7060</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>40020</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>4120</v>
+        <v>5020</v>
       </c>
       <c r="B25">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25">
-        <v>1020</v>
+        <v>10</v>
       </c>
       <c r="E25">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>4130</v>
+        <v>5110</v>
       </c>
       <c r="B26">
         <v>20</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="E26">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -1821,19 +1833,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>4140</v>
+        <v>5120</v>
       </c>
       <c r="B27">
         <v>20</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27">
-        <v>1050</v>
+        <v>1020</v>
       </c>
       <c r="E27">
-        <v>2000</v>
+        <v>40</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1844,22 +1856,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>4150</v>
+        <v>5130</v>
       </c>
       <c r="B28">
         <v>20</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28">
-        <v>1060</v>
+        <v>1030</v>
       </c>
       <c r="E28">
-        <v>5000</v>
+        <v>15</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -1867,183 +1879,183 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>5010</v>
+        <v>5140</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C29">
         <v>5</v>
       </c>
       <c r="D29">
-        <v>1031</v>
+        <v>1050</v>
       </c>
       <c r="E29">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>11010</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>5020</v>
+        <v>5150</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C30">
         <v>5</v>
       </c>
       <c r="D30">
-        <v>3010</v>
+        <v>1060</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>11020</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>5030</v>
+        <v>6010</v>
       </c>
       <c r="B31">
         <v>10</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31">
-        <v>3020</v>
+        <v>1031</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>11030</v>
+        <v>11010</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>5040</v>
+        <v>6020</v>
       </c>
       <c r="B32">
         <v>10</v>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>20</v>
+        <v>11020</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>5050</v>
+        <v>6030</v>
       </c>
       <c r="B33">
         <v>10</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>3020</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>20010</v>
+        <v>11030</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>5110</v>
+        <v>6040</v>
       </c>
       <c r="B34">
+        <v>10</v>
+      </c>
+      <c r="C34">
+        <v>6</v>
+      </c>
+      <c r="D34">
+        <v>2010</v>
+      </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
         <v>20</v>
-      </c>
-      <c r="C34">
-        <v>5</v>
-      </c>
-      <c r="D34">
-        <v>1010</v>
-      </c>
-      <c r="E34">
-        <v>15</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>5120</v>
+        <v>6050</v>
       </c>
       <c r="B35">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>1020</v>
+        <v>10</v>
       </c>
       <c r="E35">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>5130</v>
+        <v>6110</v>
       </c>
       <c r="B36">
         <v>20</v>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D36">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="E36">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -2051,19 +2063,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>5140</v>
+        <v>6120</v>
       </c>
       <c r="B37">
         <v>20</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>1050</v>
+        <v>1020</v>
       </c>
       <c r="E37">
-        <v>2500</v>
+        <v>80</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2074,22 +2086,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>5150</v>
+        <v>6130</v>
       </c>
       <c r="B38">
         <v>20</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D38">
-        <v>1060</v>
+        <v>1030</v>
       </c>
       <c r="E38">
-        <v>7500</v>
+        <v>25</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -2097,47 +2109,93 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>6040</v>
+        <v>6140</v>
       </c>
       <c r="B39">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C39">
         <v>6</v>
       </c>
       <c r="D39">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="E39">
+        <v>2500</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
         <v>5</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>6050</v>
+        <v>6150</v>
       </c>
       <c r="B40">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C40">
         <v>6</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>1060</v>
       </c>
       <c r="E40">
+        <v>7500</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>7040</v>
+      </c>
+      <c r="B41">
+        <v>10</v>
+      </c>
+      <c r="C41">
+        <v>7</v>
+      </c>
+      <c r="D41">
+        <v>2010</v>
+      </c>
+      <c r="E41">
+        <v>5</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>7050</v>
+      </c>
+      <c r="B42">
+        <v>10</v>
+      </c>
+      <c r="C42">
+        <v>7</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42">
         <v>2</v>
       </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40">
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
         <v>20010</v>
       </c>
     </row>
@@ -2150,7 +2208,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
@@ -2412,7 +2470,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>4110</v>
+        <v>5010</v>
       </c>
       <c r="B24" t="s">
         <v>32</v>
@@ -2423,7 +2481,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>4120</v>
+        <v>5020</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
@@ -2434,7 +2492,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>4130</v>
+        <v>5110</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -2445,7 +2503,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>4140</v>
+        <v>5120</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
@@ -2456,7 +2514,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>4150</v>
+        <v>5130</v>
       </c>
       <c r="B28" t="s">
         <v>36</v>
@@ -2467,7 +2525,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>5010</v>
+        <v>5140</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -2478,7 +2536,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>5020</v>
+        <v>5150</v>
       </c>
       <c r="B30" t="s">
         <v>38</v>
@@ -2489,7 +2547,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>5030</v>
+        <v>6010</v>
       </c>
       <c r="B31" t="s">
         <v>39</v>
@@ -2500,7 +2558,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>5040</v>
+        <v>6020</v>
       </c>
       <c r="B32" t="s">
         <v>40</v>
@@ -2511,7 +2569,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>5050</v>
+        <v>6030</v>
       </c>
       <c r="B33" t="s">
         <v>41</v>
@@ -2522,7 +2580,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>5110</v>
+        <v>6040</v>
       </c>
       <c r="B34" t="s">
         <v>42</v>
@@ -2533,7 +2591,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>5120</v>
+        <v>6050</v>
       </c>
       <c r="B35" t="s">
         <v>43</v>
@@ -2544,7 +2602,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>5130</v>
+        <v>6110</v>
       </c>
       <c r="B36" t="s">
         <v>44</v>
@@ -2555,7 +2613,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>5140</v>
+        <v>6120</v>
       </c>
       <c r="B37" t="s">
         <v>45</v>
@@ -2566,7 +2624,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>5150</v>
+        <v>6130</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -2577,7 +2635,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>6040</v>
+        <v>6140</v>
       </c>
       <c r="B39" t="s">
         <v>47</v>
@@ -2588,12 +2646,34 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>6050</v>
+        <v>6150</v>
       </c>
       <c r="B40" t="s">
         <v>48</v>
       </c>
       <c r="C40" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>7040</v>
+      </c>
+      <c r="B41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>7050</v>
+      </c>
+      <c r="B42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2606,7 +2686,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="15.6363636363636" customWidth="1"/>
@@ -2623,10 +2703,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2634,197 +2714,208 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>1040</v>
+        <v>1031</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2010</v>
+        <v>1060</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>7020</v>
+        <v>3020</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>7040</v>
+        <v>7020</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>7050</v>
+        <v>7040</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>7060</v>
+        <v>7050</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>7080</v>
+        <v>7060</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>8010</v>
+        <v>7080</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
+        <v>8020</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
         <v>8030</v>
       </c>
-      <c r="B20" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" t="s">
-        <v>86</v>
+      <c r="B21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -51,7 +51,7 @@
     <t>""</t>
   </si>
   <si>
-    <t>(Nu)を消費していずれかの仲間のキャラLvを上げる</t>
+    <t>アイテムを使用していずれかのキャラのLvを上げる</t>
   </si>
   <si>
     <t>編成コマンドで仲間を編成する</t>
@@ -296,10 +296,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -307,6 +307,20 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -324,69 +338,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -401,32 +354,24 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -447,12 +392,67 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -463,187 +463,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -668,6 +668,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -696,6 +720,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -715,42 +750,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -762,145 +762,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>14010</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1345,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>14010</v>
       </c>
     </row>
     <row r="6" spans="1:7">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -297,9 +297,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -318,21 +318,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -345,8 +354,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -361,24 +400,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -394,21 +433,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -421,38 +453,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -463,19 +463,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -487,163 +637,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -681,21 +681,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -714,19 +699,32 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -748,9 +746,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -762,145 +762,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>10010</v>
+        <v>14010</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1529,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1736,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:7">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -75,7 +75,7 @@
     <t>いずれかのキャラLvを3以上にする</t>
   </si>
   <si>
-    <t>バトル評価値を5%以上にする</t>
+    <t>評価値を5%以上にする</t>
   </si>
   <si>
     <t>与ダメージ累計が200を超える</t>
@@ -90,16 +90,16 @@
     <t>累計5回以上出撃する</t>
   </si>
   <si>
-    <t>累計30回以上バトルに勝利する</t>
+    <t>累計20回以上バトルに勝利する</t>
   </si>
   <si>
     <t>いずれかのキャラLvを7以上にする</t>
   </si>
   <si>
-    <t>バトル評価値を10%以上にする</t>
-  </si>
-  <si>
-    <t>与ダメージ累計が1500以上になる</t>
+    <t>評価値を10%以上にする</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が1500を超える</t>
   </si>
   <si>
     <t>月影の森のボスを撃破する</t>
@@ -129,10 +129,10 @@
     <t>いずれかのキャラLvを15以上にする</t>
   </si>
   <si>
-    <t>バトル評価値を20%以上にする</t>
-  </si>
-  <si>
-    <t>与ダメージ累計が5000以上になる</t>
+    <t>評価値を20%以上にする</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が5000を超える</t>
   </si>
   <si>
     <t>3人以上のキャラLvを15以上にする</t>
@@ -162,7 +162,7 @@
     <t>バトル評価値を25%以上にする</t>
   </si>
   <si>
-    <t>与ダメージ累計が7500以上になる</t>
+    <t>与ダメージ累計が7500を超える</t>
   </si>
   <si>
     <t>暗黒の塔のボスを撃破する</t>
@@ -296,10 +296,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -310,6 +310,59 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -317,8 +370,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,17 +394,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -354,31 +408,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -393,7 +432,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -401,54 +448,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -463,187 +463,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -654,30 +654,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -696,24 +672,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -725,6 +683,21 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -754,6 +727,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -762,16 +762,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -780,127 +780,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1592,7 +1592,7 @@
         <v>1020</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F16">
         <v>0</v>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -123,7 +123,7 @@
     <t>累計10回以上出撃する</t>
   </si>
   <si>
-    <t>累計40回以上バトルに勝利する</t>
+    <t>累計50回以上バトルに勝利する</t>
   </si>
   <si>
     <t>いずれかのキャラLvを15以上にする</t>
@@ -153,10 +153,10 @@
     <t>累計15回以上出撃する</t>
   </si>
   <si>
-    <t>累計80回以上バトルに勝利する</t>
-  </si>
-  <si>
-    <t>いずれかのキャラLvを25以上にする</t>
+    <t>累計75回以上バトルに勝利する</t>
+  </si>
+  <si>
+    <t>いずれかのキャラLvを20以上にする</t>
   </si>
   <si>
     <t>バトル評価値を25%以上にする</t>
@@ -296,10 +296,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -310,47 +310,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -358,66 +319,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -432,10 +333,48 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -447,12 +386,73 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -463,187 +463,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -654,36 +654,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -698,6 +668,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -719,6 +707,30 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -728,29 +740,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -762,145 +762,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1845,13 +1845,13 @@
         <v>1020</v>
       </c>
       <c r="E27">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1874,7 +1874,7 @@
         <v>-1</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1943,7 +1943,7 @@
         <v>3</v>
       </c>
       <c r="G31">
-        <v>11010</v>
+        <v>14020</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>11020</v>
+        <v>14020</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>11030</v>
+        <v>14020</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2075,13 +2075,13 @@
         <v>1020</v>
       </c>
       <c r="E37">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F37">
         <v>0</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2098,13 +2098,13 @@
         <v>1030</v>
       </c>
       <c r="E38">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F38">
         <v>-1</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:7">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -114,7 +114,16 @@
     <t>Rank4の重要課題を全て達成する</t>
   </si>
   <si>
-    <t>転送コマンドを利用する</t>
+    <t>3人以上のキャラLvを15以上にする</t>
+  </si>
+  <si>
+    <t>戦闘で覚醒スキルを1回以上使用する</t>
+  </si>
+  <si>
+    <t>戦闘で交代を1回以上使用する</t>
+  </si>
+  <si>
+    <t>亡国の宮殿跡地のボスを撃破する</t>
   </si>
   <si>
     <t>Rank5の重要課題を全て達成する</t>
@@ -135,16 +144,7 @@
     <t>与ダメージ累計が5000を超える</t>
   </si>
   <si>
-    <t>3人以上のキャラLvを15以上にする</t>
-  </si>
-  <si>
-    <t>戦闘で覚醒スキルを1回以上使用する</t>
-  </si>
-  <si>
-    <t>戦闘で交代を1回以上使用する</t>
-  </si>
-  <si>
-    <t>亡国の宮殿跡地のボスを撃破する</t>
+    <t>エインフェリアを1人転送する</t>
   </si>
   <si>
     <t>Rank6の重要課題を全て達成する</t>
@@ -296,10 +296,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -325,36 +325,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -362,11 +332,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -379,6 +348,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -386,9 +363,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -403,12 +379,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -416,15 +393,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -438,9 +424,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -453,6 +438,21 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -463,187 +463,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -654,6 +654,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -677,39 +686,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -740,6 +716,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -754,6 +739,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -762,145 +762,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1773,16 +1773,16 @@
         <v>5</v>
       </c>
       <c r="D24">
-        <v>7060</v>
+        <v>1031</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>40020</v>
+        <v>14020</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1796,90 +1796,90 @@
         <v>5</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>3010</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>20010</v>
+        <v>14020</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>5110</v>
+        <v>5030</v>
       </c>
       <c r="B26">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C26">
         <v>5</v>
       </c>
       <c r="D26">
-        <v>1010</v>
+        <v>3020</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>14020</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>5120</v>
+        <v>5040</v>
       </c>
       <c r="B27">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C27">
         <v>5</v>
       </c>
       <c r="D27">
-        <v>1020</v>
+        <v>2010</v>
       </c>
       <c r="E27">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>5130</v>
+        <v>5050</v>
       </c>
       <c r="B28">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C28">
         <v>5</v>
       </c>
       <c r="D28">
-        <v>1030</v>
+        <v>10</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>5140</v>
+        <v>5110</v>
       </c>
       <c r="B29">
         <v>20</v>
@@ -1888,10 +1888,10 @@
         <v>5</v>
       </c>
       <c r="D29">
-        <v>1050</v>
+        <v>1010</v>
       </c>
       <c r="E29">
-        <v>2000</v>
+        <v>10</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>5150</v>
+        <v>5120</v>
       </c>
       <c r="B30">
         <v>20</v>
@@ -1911,10 +1911,10 @@
         <v>5</v>
       </c>
       <c r="D30">
-        <v>1060</v>
+        <v>1020</v>
       </c>
       <c r="E30">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1925,76 +1925,76 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>6010</v>
+        <v>5130</v>
       </c>
       <c r="B31">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E31">
         <v>15</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="G31">
-        <v>14020</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>6020</v>
+        <v>5140</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32">
-        <v>3010</v>
+        <v>1050</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>14020</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>6030</v>
+        <v>5150</v>
       </c>
       <c r="B33">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>3020</v>
+        <v>1060</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>14020</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>6040</v>
+        <v>6010</v>
       </c>
       <c r="B34">
         <v>10</v>
@@ -2003,21 +2003,21 @@
         <v>6</v>
       </c>
       <c r="D34">
-        <v>2010</v>
+        <v>7060</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>20</v>
+        <v>40020</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>6050</v>
+        <v>6020</v>
       </c>
       <c r="B35">
         <v>10</v>
@@ -2492,7 +2492,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>5110</v>
+        <v>5030</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -2503,7 +2503,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>5120</v>
+        <v>5040</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>5130</v>
+        <v>5050</v>
       </c>
       <c r="B28" t="s">
         <v>36</v>
@@ -2525,7 +2525,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>5140</v>
+        <v>5110</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -2536,7 +2536,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>5150</v>
+        <v>5120</v>
       </c>
       <c r="B30" t="s">
         <v>38</v>
@@ -2547,7 +2547,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>6010</v>
+        <v>5130</v>
       </c>
       <c r="B31" t="s">
         <v>39</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>6020</v>
+        <v>5140</v>
       </c>
       <c r="B32" t="s">
         <v>40</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>6030</v>
+        <v>5150</v>
       </c>
       <c r="B33" t="s">
         <v>41</v>
@@ -2580,7 +2580,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>6040</v>
+        <v>6010</v>
       </c>
       <c r="B34" t="s">
         <v>42</v>
@@ -2591,7 +2591,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>6050</v>
+        <v>6020</v>
       </c>
       <c r="B35" t="s">
         <v>43</v>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -297,8 +297,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -310,25 +310,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -339,16 +325,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -356,10 +334,17 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -379,13 +364,42 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -401,21 +415,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -425,15 +424,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -447,10 +438,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -463,19 +463,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -487,163 +643,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -657,11 +657,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -685,22 +706,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -725,21 +731,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -754,6 +745,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -762,7 +762,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -771,7 +771,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -780,127 +780,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="106">
   <si>
     <t>Id</t>
   </si>
@@ -117,10 +117,10 @@
     <t>3人以上のキャラLvを15以上にする</t>
   </si>
   <si>
-    <t>戦闘で覚醒スキルを1回以上使用する</t>
-  </si>
-  <si>
-    <t>戦闘で交代を1回以上使用する</t>
+    <t>バトルで覚醒スキルを1回以上使用する</t>
+  </si>
+  <si>
+    <t>バトルで交代を1回以上使用する</t>
   </si>
   <si>
     <t>亡国の宮殿跡地のボスを撃破する</t>
@@ -159,18 +159,57 @@
     <t>いずれかのキャラLvを20以上にする</t>
   </si>
   <si>
-    <t>バトル評価値を25%以上にする</t>
+    <t>評価値を25%以上にする</t>
   </si>
   <si>
     <t>与ダメージ累計が7500を超える</t>
   </si>
   <si>
+    <t>いずれかのキャラをクラスチェンジする</t>
+  </si>
+  <si>
     <t>暗黒の塔のボスを撃破する</t>
   </si>
   <si>
     <t>Rank7の重要課題を全て達成する</t>
   </si>
   <si>
+    <t>3人以上のキャラLvを25以上にする</t>
+  </si>
+  <si>
+    <t>バトルで覚醒スキルを5回以上使用する</t>
+  </si>
+  <si>
+    <t>バトルで交代を5回以上使用する</t>
+  </si>
+  <si>
+    <t>Rank8の重要課題を全て達成する</t>
+  </si>
+  <si>
+    <t>5人以上のキャラLvを25以上にする</t>
+  </si>
+  <si>
+    <t>エインフェリアを2人転送する</t>
+  </si>
+  <si>
+    <t>3人以上のキャラをクラスチェンジする</t>
+  </si>
+  <si>
+    <t>ラグナロクで勝利する</t>
+  </si>
+  <si>
+    <t>Rank9の重要課題を全て達成する</t>
+  </si>
+  <si>
+    <t>5人以上のキャラLvを30以上にする</t>
+  </si>
+  <si>
+    <t>エインフェリアを3人転送する</t>
+  </si>
+  <si>
+    <t>5人以上のキャラをクラスチェンジする</t>
+  </si>
+  <si>
     <t>Complete</t>
   </si>
   <si>
@@ -223,6 +262,12 @@
   </si>
   <si>
     <t>与ダメージ</t>
+  </si>
+  <si>
+    <t>ClassChangeCount</t>
+  </si>
+  <si>
+    <t>クラスチェンジキャラ数</t>
   </si>
   <si>
     <t>ClearStage</t>
@@ -296,8 +341,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -310,9 +355,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,39 +407,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -378,53 +459,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -439,15 +492,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -463,7 +508,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -475,13 +544,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -493,13 +574,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,19 +628,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,97 +682,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -657,17 +702,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -687,17 +741,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -725,8 +779,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -745,15 +799,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -762,145 +807,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1227,7 +1272,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9.54545454545454"/>
@@ -2155,7 +2200,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>7040</v>
+        <v>7010</v>
       </c>
       <c r="B41">
         <v>10</v>
@@ -2164,21 +2209,21 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>2010</v>
+        <v>1070</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41">
-        <v>25</v>
+        <v>14310</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>7050</v>
+        <v>7020</v>
       </c>
       <c r="B42">
         <v>10</v>
@@ -2187,16 +2232,338 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>7030</v>
+      </c>
+      <c r="B43">
+        <v>10</v>
+      </c>
+      <c r="C43">
+        <v>7</v>
+      </c>
+      <c r="D43">
+        <v>10</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
         <v>20010</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>7110</v>
+      </c>
+      <c r="B44">
+        <v>20</v>
+      </c>
+      <c r="C44">
+        <v>7</v>
+      </c>
+      <c r="D44">
+        <v>1031</v>
+      </c>
+      <c r="E44">
+        <v>25</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>7120</v>
+      </c>
+      <c r="B45">
+        <v>20</v>
+      </c>
+      <c r="C45">
+        <v>7</v>
+      </c>
+      <c r="D45">
+        <v>3010</v>
+      </c>
+      <c r="E45">
+        <v>5</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>7130</v>
+      </c>
+      <c r="B46">
+        <v>20</v>
+      </c>
+      <c r="C46">
+        <v>7</v>
+      </c>
+      <c r="D46">
+        <v>3020</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>8010</v>
+      </c>
+      <c r="B47">
+        <v>10</v>
+      </c>
+      <c r="C47">
+        <v>8</v>
+      </c>
+      <c r="D47">
+        <v>1012</v>
+      </c>
+      <c r="E47">
+        <v>2</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>8020</v>
+      </c>
+      <c r="B48">
+        <v>10</v>
+      </c>
+      <c r="C48">
+        <v>8</v>
+      </c>
+      <c r="D48">
+        <v>10</v>
+      </c>
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>20010</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>8110</v>
+      </c>
+      <c r="B49">
+        <v>20</v>
+      </c>
+      <c r="C49">
+        <v>8</v>
+      </c>
+      <c r="D49">
+        <v>1031</v>
+      </c>
+      <c r="E49">
+        <v>25</v>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>8120</v>
+      </c>
+      <c r="B50">
+        <v>20</v>
+      </c>
+      <c r="C50">
+        <v>8</v>
+      </c>
+      <c r="D50">
+        <v>7060</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>8130</v>
+      </c>
+      <c r="B51">
+        <v>20</v>
+      </c>
+      <c r="C51">
+        <v>8</v>
+      </c>
+      <c r="D51">
+        <v>1070</v>
+      </c>
+      <c r="E51">
+        <v>3</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>9010</v>
+      </c>
+      <c r="B52">
+        <v>10</v>
+      </c>
+      <c r="C52">
+        <v>9</v>
+      </c>
+      <c r="D52">
+        <v>2010</v>
+      </c>
+      <c r="E52">
+        <v>203</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>9020</v>
+      </c>
+      <c r="B53">
+        <v>10</v>
+      </c>
+      <c r="C53">
+        <v>9</v>
+      </c>
+      <c r="D53">
+        <v>10</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>20010</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>9110</v>
+      </c>
+      <c r="B54">
+        <v>20</v>
+      </c>
+      <c r="C54">
+        <v>9</v>
+      </c>
+      <c r="D54">
+        <v>1031</v>
+      </c>
+      <c r="E54">
+        <v>30</v>
+      </c>
+      <c r="F54">
+        <v>5</v>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>9120</v>
+      </c>
+      <c r="B55">
+        <v>20</v>
+      </c>
+      <c r="C55">
+        <v>9</v>
+      </c>
+      <c r="D55">
+        <v>7060</v>
+      </c>
+      <c r="E55">
+        <v>3</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>9130</v>
+      </c>
+      <c r="B56">
+        <v>20</v>
+      </c>
+      <c r="C56">
+        <v>9</v>
+      </c>
+      <c r="D56">
+        <v>1070</v>
+      </c>
+      <c r="E56">
+        <v>5</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2208,7 +2575,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
@@ -2657,7 +3024,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>7040</v>
+        <v>7010</v>
       </c>
       <c r="B41" t="s">
         <v>49</v>
@@ -2668,12 +3035,166 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>7050</v>
+        <v>7020</v>
       </c>
       <c r="B42" t="s">
         <v>50</v>
       </c>
       <c r="C42" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>7030</v>
+      </c>
+      <c r="B43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>7110</v>
+      </c>
+      <c r="B44" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>7120</v>
+      </c>
+      <c r="B45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>7130</v>
+      </c>
+      <c r="B46" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>8010</v>
+      </c>
+      <c r="B47" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>8020</v>
+      </c>
+      <c r="B48" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>8110</v>
+      </c>
+      <c r="B49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>8120</v>
+      </c>
+      <c r="B50" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>8130</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>9010</v>
+      </c>
+      <c r="B52" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>9020</v>
+      </c>
+      <c r="B53" t="s">
+        <v>60</v>
+      </c>
+      <c r="C53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>9110</v>
+      </c>
+      <c r="B54" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>9120</v>
+      </c>
+      <c r="B55" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>9130</v>
+      </c>
+      <c r="B56" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2686,7 +3207,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="15.6363636363636" customWidth="1"/>
@@ -2703,10 +3224,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2714,10 +3235,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2725,10 +3246,10 @@
         <v>1012</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2736,10 +3257,10 @@
         <v>1020</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2747,10 +3268,10 @@
         <v>1030</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2758,10 +3279,10 @@
         <v>1031</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2769,10 +3290,10 @@
         <v>1040</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2780,10 +3301,10 @@
         <v>1050</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2791,131 +3312,142 @@
         <v>1060</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>2010</v>
+        <v>1070</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>7020</v>
+        <v>3020</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>7040</v>
+        <v>7020</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>7050</v>
+        <v>7040</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>7060</v>
+        <v>7050</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>7080</v>
+        <v>7060</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>8010</v>
+        <v>7080</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
+        <v>8020</v>
+      </c>
+      <c r="B21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
         <v>8030</v>
       </c>
-      <c r="B21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" t="s">
-        <v>90</v>
+      <c r="B22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -342,9 +342,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -356,31 +356,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -401,14 +384,46 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -422,38 +437,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -468,6 +461,14 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -475,9 +476,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -485,17 +486,16 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -508,7 +508,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,61 +586,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -592,13 +646,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -610,13 +658,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -628,31 +676,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -664,31 +688,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -699,6 +699,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -713,15 +737,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -741,17 +756,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -775,30 +799,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -807,16 +807,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -825,127 +825,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>10010</v>
+        <v>11010</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>10020</v>
+        <v>11020</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1666,7 +1666,7 @@
         <v>-1</v>
       </c>
       <c r="G17">
-        <v>10030</v>
+        <v>11030</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>10040</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1712,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>10050</v>
+        <v>11050</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>14020</v>
+        <v>14310</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1873,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>14020</v>
+        <v>15040</v>
       </c>
     </row>
     <row r="27" spans="1:7">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -355,8 +355,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -370,7 +393,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -383,47 +406,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -431,6 +416,20 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -444,9 +443,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -454,14 +461,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -492,8 +491,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -505,6 +505,24 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -520,19 +538,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -544,13 +556,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -562,37 +628,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -610,7 +646,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -622,73 +688,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -699,30 +699,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -756,6 +732,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -782,15 +776,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -799,6 +784,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -807,7 +807,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -816,136 +816,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>11010</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>11020</v>
+        <v>10020</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1666,7 +1666,7 @@
         <v>-1</v>
       </c>
       <c r="G17">
-        <v>11030</v>
+        <v>10030</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>11040</v>
+        <v>10040</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1712,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>11050</v>
+        <v>10050</v>
       </c>
     </row>
     <row r="20" spans="1:7">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -355,9 +355,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -370,16 +377,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -392,6 +429,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -399,8 +444,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -414,32 +468,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -453,47 +486,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -508,25 +508,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -544,7 +568,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -556,19 +598,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,7 +658,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -592,43 +670,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -640,49 +682,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -702,32 +702,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -741,11 +731,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -774,13 +770,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -807,7 +807,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -816,7 +816,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -825,127 +825,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>14010</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -343,8 +343,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -355,14 +355,68 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -371,7 +425,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -394,13 +463,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -408,22 +470,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -437,63 +491,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -508,31 +508,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,6 +526,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -562,7 +550,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,31 +604,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -610,31 +616,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,13 +646,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,7 +664,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,13 +688,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -702,31 +702,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -742,6 +728,48 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -763,39 +791,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -807,7 +807,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -816,7 +816,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -825,127 +825,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1735,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>15040</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>14310</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1873,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>15040</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>15040</v>
       </c>
     </row>
     <row r="48" spans="1:7">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -341,8 +341,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -355,6 +355,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -363,38 +370,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -402,82 +377,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -492,8 +393,107 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -508,13 +508,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -526,13 +526,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -544,7 +592,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -556,19 +604,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,19 +622,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -610,7 +652,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -622,25 +664,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,43 +676,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -699,60 +699,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -789,6 +735,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -799,6 +784,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -807,145 +807,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1735,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>15040</v>
+        <v>15050</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>15040</v>
+        <v>15050</v>
       </c>
     </row>
     <row r="48" spans="1:7">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -341,10 +341,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -356,22 +356,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -384,32 +376,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -424,6 +408,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -431,22 +422,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -463,6 +446,29 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -471,9 +477,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -485,15 +491,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -508,7 +508,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,7 +526,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -532,7 +544,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -544,7 +592,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -556,13 +610,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,91 +670,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,19 +682,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -699,39 +699,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -768,19 +735,41 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -799,6 +788,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -807,145 +807,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1827,7 +1827,7 @@
         <v>3</v>
       </c>
       <c r="G24">
-        <v>14020</v>
+        <v>15060</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>1110</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>20</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="28" spans="1:7">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8410"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -341,10 +341,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -355,10 +355,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -370,15 +387,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -393,60 +424,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -461,7 +446,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -477,14 +485,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -493,9 +493,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -508,7 +508,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,13 +526,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -538,7 +556,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,7 +592,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -562,31 +628,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,49 +640,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -658,19 +664,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,13 +688,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -699,54 +699,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -767,9 +719,59 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -791,11 +793,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -807,145 +807,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>14010</v>
+        <v>15050</v>
       </c>
     </row>
     <row r="4" spans="1:7">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -75,72 +75,72 @@
     <t>いずれかのキャラLvを3以上にする</t>
   </si>
   <si>
+    <t>評価値を3%以上にする</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が200を超える</t>
+  </si>
+  <si>
+    <t>忘れられた山岳遺跡のボスを撃破する</t>
+  </si>
+  <si>
+    <t>Rank2の重要課題を全て達成する</t>
+  </si>
+  <si>
+    <t>累計5回以上出撃する</t>
+  </si>
+  <si>
+    <t>累計20回以上バトルに勝利する</t>
+  </si>
+  <si>
+    <t>いずれかのキャラLvを7以上にする</t>
+  </si>
+  <si>
     <t>評価値を5%以上にする</t>
   </si>
   <si>
-    <t>与ダメージ累計が200を超える</t>
-  </si>
-  <si>
-    <t>忘れられた山岳遺跡のボスを撃破する</t>
-  </si>
-  <si>
-    <t>Rank2の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>累計5回以上出撃する</t>
-  </si>
-  <si>
-    <t>累計20回以上バトルに勝利する</t>
-  </si>
-  <si>
-    <t>いずれかのキャラLvを7以上にする</t>
+    <t>与ダメージ累計が1500を超える</t>
+  </si>
+  <si>
+    <t>月影の森のボスを撃破する</t>
+  </si>
+  <si>
+    <t>Rank3の重要課題を全て達成する</t>
+  </si>
+  <si>
+    <t>戦争(BattleField)ステージに出撃する</t>
+  </si>
+  <si>
+    <t>Rank4の重要課題を全て達成する</t>
+  </si>
+  <si>
+    <t>3人以上のキャラLvを15以上にする</t>
+  </si>
+  <si>
+    <t>バトルで覚醒スキルを1回以上使用する</t>
+  </si>
+  <si>
+    <t>バトルで交代を1回以上使用する</t>
+  </si>
+  <si>
+    <t>亡国の宮殿跡地のボスを撃破する</t>
+  </si>
+  <si>
+    <t>Rank5の重要課題を全て達成する</t>
+  </si>
+  <si>
+    <t>累計10回以上出撃する</t>
+  </si>
+  <si>
+    <t>累計50回以上バトルに勝利する</t>
+  </si>
+  <si>
+    <t>いずれかのキャラLvを15以上にする</t>
   </si>
   <si>
     <t>評価値を10%以上にする</t>
   </si>
   <si>
-    <t>与ダメージ累計が1500を超える</t>
-  </si>
-  <si>
-    <t>月影の森のボスを撃破する</t>
-  </si>
-  <si>
-    <t>Rank3の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>戦争(BattleField)ステージに出撃する</t>
-  </si>
-  <si>
-    <t>Rank4の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>3人以上のキャラLvを15以上にする</t>
-  </si>
-  <si>
-    <t>バトルで覚醒スキルを1回以上使用する</t>
-  </si>
-  <si>
-    <t>バトルで交代を1回以上使用する</t>
-  </si>
-  <si>
-    <t>亡国の宮殿跡地のボスを撃破する</t>
-  </si>
-  <si>
-    <t>Rank5の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>累計10回以上出撃する</t>
-  </si>
-  <si>
-    <t>累計50回以上バトルに勝利する</t>
-  </si>
-  <si>
-    <t>いずれかのキャラLvを15以上にする</t>
-  </si>
-  <si>
-    <t>評価値を20%以上にする</t>
-  </si>
-  <si>
     <t>与ダメージ累計が5000を超える</t>
   </si>
   <si>
@@ -159,7 +159,7 @@
     <t>いずれかのキャラLvを20以上にする</t>
   </si>
   <si>
-    <t>評価値を25%以上にする</t>
+    <t>評価値を15%以上にする</t>
   </si>
   <si>
     <t>与ダメージ累計が7500を超える</t>
@@ -342,9 +342,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -352,6 +352,20 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -363,9 +377,59 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -379,59 +443,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -445,31 +459,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -485,17 +485,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -508,7 +508,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,7 +574,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -538,7 +598,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,67 +628,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -628,67 +688,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -717,13 +717,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -743,17 +747,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -763,15 +761,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -799,6 +788,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -807,16 +807,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -825,127 +825,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1522,7 +1522,7 @@
         <v>1050</v>
       </c>
       <c r="E11">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1683,7 +1683,7 @@
         <v>1050</v>
       </c>
       <c r="E18">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2005,7 +2005,7 @@
         <v>1050</v>
       </c>
       <c r="E32">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2166,7 +2166,7 @@
         <v>1050</v>
       </c>
       <c r="E39">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="F39">
         <v>0</v>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="112">
   <si>
     <t>Id</t>
   </si>
@@ -84,6 +84,9 @@
     <t>忘れられた山岳遺跡のボスを撃破する</t>
   </si>
   <si>
+    <t>仲間の封印魔法を2つ以上解放する</t>
+  </si>
+  <si>
     <t>Rank2の重要課題を全て達成する</t>
   </si>
   <si>
@@ -105,6 +108,9 @@
     <t>月影の森のボスを撃破する</t>
   </si>
   <si>
+    <t>仲間の封印魔法を4つ以上解放する</t>
+  </si>
+  <si>
     <t>Rank3の重要課題を全て達成する</t>
   </si>
   <si>
@@ -126,6 +132,9 @@
     <t>亡国の宮殿跡地のボスを撃破する</t>
   </si>
   <si>
+    <t>仲間の封印魔法を6つ以上解放する</t>
+  </si>
+  <si>
     <t>Rank5の重要課題を全て達成する</t>
   </si>
   <si>
@@ -171,6 +180,9 @@
     <t>暗黒の塔のボスを撃破する</t>
   </si>
   <si>
+    <t>仲間の封印魔法を8つ以上解放する</t>
+  </si>
+  <si>
     <t>Rank7の重要課題を全て達成する</t>
   </si>
   <si>
@@ -183,6 +195,9 @@
     <t>バトルで交代を5回以上使用する</t>
   </si>
   <si>
+    <t>天空城のボスを撃破する</t>
+  </si>
+  <si>
     <t>Rank8の重要課題を全て達成する</t>
   </si>
   <si>
@@ -195,9 +210,6 @@
     <t>3人以上のキャラをクラスチェンジする</t>
   </si>
   <si>
-    <t>ラグナロクで勝利する</t>
-  </si>
-  <si>
     <t>Rank9の重要課題を全て達成する</t>
   </si>
   <si>
@@ -268,6 +280,12 @@
   </si>
   <si>
     <t>クラスチェンジキャラ数</t>
+  </si>
+  <si>
+    <t>LearnSkillCount</t>
+  </si>
+  <si>
+    <t>封印魔法解放数</t>
   </si>
   <si>
     <t>ClearStage</t>
@@ -341,10 +359,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -369,6 +387,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -386,48 +411,13 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -436,23 +426,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -468,6 +450,22 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -475,7 +473,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -483,17 +510,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -514,7 +532,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -532,13 +568,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,13 +580,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -568,7 +604,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,61 +682,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -646,49 +700,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -732,17 +750,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -750,8 +764,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -780,22 +794,26 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -807,145 +825,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1272,7 +1290,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9.54545454545454"/>
@@ -1588,7 +1606,7 @@
         <v>2</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>1080</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -1597,35 +1615,35 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>20010</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>3010</v>
+        <v>2080</v>
       </c>
       <c r="B15">
         <v>10</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>10010</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B16">
         <v>10</v>
@@ -1634,21 +1652,21 @@
         <v>3</v>
       </c>
       <c r="D16">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>10020</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B17">
         <v>10</v>
@@ -1657,21 +1675,21 @@
         <v>3</v>
       </c>
       <c r="D17">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="E17">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>10030</v>
+        <v>10020</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B18">
         <v>10</v>
@@ -1680,21 +1698,21 @@
         <v>3</v>
       </c>
       <c r="D18">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="E18">
-        <v>500</v>
+        <v>7</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G18">
-        <v>10040</v>
+        <v>10030</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>3050</v>
+        <v>3040</v>
       </c>
       <c r="B19">
         <v>10</v>
@@ -1703,21 +1721,21 @@
         <v>3</v>
       </c>
       <c r="D19">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="E19">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>10050</v>
+        <v>10040</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>3060</v>
+        <v>3050</v>
       </c>
       <c r="B20">
         <v>10</v>
@@ -1726,21 +1744,21 @@
         <v>3</v>
       </c>
       <c r="D20">
-        <v>2010</v>
+        <v>1060</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>1500</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>15050</v>
+        <v>10050</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>3070</v>
+        <v>3060</v>
       </c>
       <c r="B21">
         <v>10</v>
@@ -1749,50 +1767,50 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>20010</v>
+        <v>15050</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>4010</v>
+        <v>3070</v>
       </c>
       <c r="B22">
         <v>10</v>
       </c>
       <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>1080</v>
+      </c>
+      <c r="E22">
         <v>4</v>
       </c>
-      <c r="D22">
-        <v>1012</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>5</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>4020</v>
+        <v>3080</v>
       </c>
       <c r="B23">
         <v>10</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23">
         <v>10</v>
@@ -1809,53 +1827,53 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="B24">
         <v>10</v>
       </c>
       <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24">
+        <v>1012</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
         <v>5</v>
-      </c>
-      <c r="D24">
-        <v>1031</v>
-      </c>
-      <c r="E24">
-        <v>15</v>
-      </c>
-      <c r="F24">
-        <v>3</v>
-      </c>
-      <c r="G24">
-        <v>15060</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>5020</v>
+        <v>4020</v>
       </c>
       <c r="B25">
         <v>10</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25">
-        <v>3010</v>
+        <v>10</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>5030</v>
+        <v>5010</v>
       </c>
       <c r="B26">
         <v>10</v>
@@ -1864,21 +1882,21 @@
         <v>5</v>
       </c>
       <c r="D26">
-        <v>3020</v>
+        <v>1031</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>15060</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>5040</v>
+        <v>5020</v>
       </c>
       <c r="B27">
         <v>10</v>
@@ -1887,21 +1905,21 @@
         <v>5</v>
       </c>
       <c r="D27">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>1110</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>5050</v>
+        <v>5030</v>
       </c>
       <c r="B28">
         <v>10</v>
@@ -1910,90 +1928,90 @@
         <v>5</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>3020</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>20010</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>5110</v>
+        <v>5040</v>
       </c>
       <c r="B29">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C29">
         <v>5</v>
       </c>
       <c r="D29">
-        <v>1010</v>
+        <v>2010</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>5120</v>
+        <v>5050</v>
       </c>
       <c r="B30">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C30">
         <v>5</v>
       </c>
       <c r="D30">
-        <v>1020</v>
+        <v>1080</v>
       </c>
       <c r="E30">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>5130</v>
+        <v>5060</v>
       </c>
       <c r="B31">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C31">
         <v>5</v>
       </c>
       <c r="D31">
-        <v>1030</v>
+        <v>10</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>5140</v>
+        <v>5110</v>
       </c>
       <c r="B32">
         <v>20</v>
@@ -2002,10 +2020,10 @@
         <v>5</v>
       </c>
       <c r="D32">
-        <v>1050</v>
+        <v>1010</v>
       </c>
       <c r="E32">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2016,7 +2034,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>5150</v>
+        <v>5120</v>
       </c>
       <c r="B33">
         <v>20</v>
@@ -2025,10 +2043,10 @@
         <v>5</v>
       </c>
       <c r="D33">
-        <v>1060</v>
+        <v>1020</v>
       </c>
       <c r="E33">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2039,65 +2057,65 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>6010</v>
+        <v>5130</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34">
-        <v>7060</v>
+        <v>1030</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G34">
-        <v>40020</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>6020</v>
+        <v>5140</v>
       </c>
       <c r="B35">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35">
-        <v>10</v>
+        <v>1050</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>20010</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>6110</v>
+        <v>5150</v>
       </c>
       <c r="B36">
         <v>20</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36">
-        <v>1010</v>
+        <v>1060</v>
       </c>
       <c r="E36">
-        <v>15</v>
+        <v>5000</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2108,53 +2126,53 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>6120</v>
+        <v>6010</v>
       </c>
       <c r="B37">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C37">
         <v>6</v>
       </c>
       <c r="D37">
-        <v>1020</v>
+        <v>7060</v>
       </c>
       <c r="E37">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="F37">
         <v>0</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>40020</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>6130</v>
+        <v>6020</v>
       </c>
       <c r="B38">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C38">
         <v>6</v>
       </c>
       <c r="D38">
-        <v>1030</v>
+        <v>10</v>
       </c>
       <c r="E38">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>6140</v>
+        <v>6110</v>
       </c>
       <c r="B39">
         <v>20</v>
@@ -2163,10 +2181,10 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>1050</v>
+        <v>1010</v>
       </c>
       <c r="E39">
-        <v>1500</v>
+        <v>15</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2177,7 +2195,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>6150</v>
+        <v>6120</v>
       </c>
       <c r="B40">
         <v>20</v>
@@ -2186,10 +2204,10 @@
         <v>6</v>
       </c>
       <c r="D40">
-        <v>1060</v>
+        <v>1020</v>
       </c>
       <c r="E40">
-        <v>7500</v>
+        <v>75</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2200,108 +2218,108 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>7010</v>
+        <v>6130</v>
       </c>
       <c r="B41">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D41">
-        <v>1070</v>
+        <v>1030</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G41">
-        <v>14310</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>7020</v>
+        <v>6140</v>
       </c>
       <c r="B42">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D42">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>1500</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>7030</v>
+        <v>6150</v>
       </c>
       <c r="B43">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D43">
-        <v>10</v>
+        <v>1060</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>7500</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43">
-        <v>20010</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>7110</v>
+        <v>7010</v>
       </c>
       <c r="B44">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C44">
         <v>7</v>
       </c>
       <c r="D44">
-        <v>1031</v>
+        <v>1070</v>
       </c>
       <c r="E44">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>14310</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>7120</v>
+        <v>7020</v>
       </c>
       <c r="B45">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C45">
         <v>7</v>
       </c>
       <c r="D45">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="E45">
         <v>5</v>
@@ -2310,44 +2328,44 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>7130</v>
+        <v>7030</v>
       </c>
       <c r="B46">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C46">
         <v>7</v>
       </c>
       <c r="D46">
-        <v>3020</v>
+        <v>1080</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F46">
         <v>0</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>8010</v>
+        <v>7040</v>
       </c>
       <c r="B47">
         <v>10</v>
       </c>
       <c r="C47">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D47">
-        <v>1012</v>
+        <v>10</v>
       </c>
       <c r="E47">
         <v>2</v>
@@ -2356,50 +2374,50 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>15050</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>8020</v>
+        <v>7110</v>
       </c>
       <c r="B48">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C48">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>1031</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G48">
-        <v>20010</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>8110</v>
+        <v>7120</v>
       </c>
       <c r="B49">
         <v>20</v>
       </c>
       <c r="C49">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D49">
-        <v>1031</v>
+        <v>3010</v>
       </c>
       <c r="E49">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F49">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G49">
         <v>2</v>
@@ -2407,19 +2425,19 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>8120</v>
+        <v>7130</v>
       </c>
       <c r="B50">
         <v>20</v>
       </c>
       <c r="C50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D50">
-        <v>7060</v>
+        <v>3020</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2430,91 +2448,91 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>8130</v>
+        <v>8010</v>
       </c>
       <c r="B51">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C51">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D51">
-        <v>1070</v>
+        <v>2010</v>
       </c>
       <c r="E51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>9010</v>
+        <v>8020</v>
       </c>
       <c r="B52">
         <v>10</v>
       </c>
       <c r="C52">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D52">
-        <v>2010</v>
+        <v>10</v>
       </c>
       <c r="E52">
-        <v>203</v>
+        <v>2</v>
       </c>
       <c r="F52">
         <v>0</v>
       </c>
       <c r="G52">
-        <v>30</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>9020</v>
+        <v>8110</v>
       </c>
       <c r="B53">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C53">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>1031</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G53">
-        <v>20010</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>9110</v>
+        <v>8120</v>
       </c>
       <c r="B54">
         <v>20</v>
       </c>
       <c r="C54">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D54">
-        <v>1031</v>
+        <v>7060</v>
       </c>
       <c r="E54">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -2522,16 +2540,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>9120</v>
+        <v>8130</v>
       </c>
       <c r="B55">
         <v>20</v>
       </c>
       <c r="C55">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D55">
-        <v>7060</v>
+        <v>1070</v>
       </c>
       <c r="E55">
         <v>3</v>
@@ -2545,24 +2563,116 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
+        <v>9010</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+      <c r="C56">
+        <v>8</v>
+      </c>
+      <c r="D56">
+        <v>1012</v>
+      </c>
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>15050</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>9020</v>
+      </c>
+      <c r="B57">
+        <v>10</v>
+      </c>
+      <c r="C57">
+        <v>9</v>
+      </c>
+      <c r="D57">
+        <v>10</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>20010</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>9110</v>
+      </c>
+      <c r="B58">
+        <v>20</v>
+      </c>
+      <c r="C58">
+        <v>9</v>
+      </c>
+      <c r="D58">
+        <v>1031</v>
+      </c>
+      <c r="E58">
+        <v>30</v>
+      </c>
+      <c r="F58">
+        <v>5</v>
+      </c>
+      <c r="G58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>9120</v>
+      </c>
+      <c r="B59">
+        <v>20</v>
+      </c>
+      <c r="C59">
+        <v>9</v>
+      </c>
+      <c r="D59">
+        <v>7060</v>
+      </c>
+      <c r="E59">
+        <v>3</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
         <v>9130</v>
       </c>
-      <c r="B56">
+      <c r="B60">
         <v>20</v>
       </c>
-      <c r="C56">
+      <c r="C60">
         <v>9</v>
       </c>
-      <c r="D56">
+      <c r="D60">
         <v>1070</v>
       </c>
-      <c r="E56">
+      <c r="E60">
         <v>5</v>
       </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56">
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
         <v>2</v>
       </c>
     </row>
@@ -2575,7 +2685,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
@@ -2738,7 +2848,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>3010</v>
+        <v>2080</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
@@ -2749,7 +2859,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
@@ -2760,7 +2870,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B17" t="s">
         <v>25</v>
@@ -2771,7 +2881,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
@@ -2782,7 +2892,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>3050</v>
+        <v>3040</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
@@ -2793,7 +2903,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>3060</v>
+        <v>3050</v>
       </c>
       <c r="B20" t="s">
         <v>28</v>
@@ -2804,7 +2914,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>3070</v>
+        <v>3060</v>
       </c>
       <c r="B21" t="s">
         <v>29</v>
@@ -2815,7 +2925,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>4010</v>
+        <v>3070</v>
       </c>
       <c r="B22" t="s">
         <v>30</v>
@@ -2826,7 +2936,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>4020</v>
+        <v>3080</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -2837,7 +2947,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="B24" t="s">
         <v>32</v>
@@ -2848,7 +2958,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>5020</v>
+        <v>4020</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
@@ -2859,7 +2969,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>5030</v>
+        <v>5010</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -2870,7 +2980,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>5040</v>
+        <v>5020</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
@@ -2881,7 +2991,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>5050</v>
+        <v>5030</v>
       </c>
       <c r="B28" t="s">
         <v>36</v>
@@ -2892,7 +3002,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>5110</v>
+        <v>5040</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -2903,7 +3013,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>5120</v>
+        <v>5050</v>
       </c>
       <c r="B30" t="s">
         <v>38</v>
@@ -2914,7 +3024,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>5130</v>
+        <v>5060</v>
       </c>
       <c r="B31" t="s">
         <v>39</v>
@@ -2925,7 +3035,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>5140</v>
+        <v>5110</v>
       </c>
       <c r="B32" t="s">
         <v>40</v>
@@ -2936,7 +3046,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>5150</v>
+        <v>5120</v>
       </c>
       <c r="B33" t="s">
         <v>41</v>
@@ -2947,7 +3057,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>6010</v>
+        <v>5130</v>
       </c>
       <c r="B34" t="s">
         <v>42</v>
@@ -2958,7 +3068,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>6020</v>
+        <v>5140</v>
       </c>
       <c r="B35" t="s">
         <v>43</v>
@@ -2969,7 +3079,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>6110</v>
+        <v>5150</v>
       </c>
       <c r="B36" t="s">
         <v>44</v>
@@ -2980,7 +3090,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>6120</v>
+        <v>6010</v>
       </c>
       <c r="B37" t="s">
         <v>45</v>
@@ -2991,7 +3101,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>6130</v>
+        <v>6020</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -3002,7 +3112,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>6140</v>
+        <v>6110</v>
       </c>
       <c r="B39" t="s">
         <v>47</v>
@@ -3013,7 +3123,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>6150</v>
+        <v>6120</v>
       </c>
       <c r="B40" t="s">
         <v>48</v>
@@ -3024,7 +3134,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>7010</v>
+        <v>6130</v>
       </c>
       <c r="B41" t="s">
         <v>49</v>
@@ -3035,7 +3145,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>7020</v>
+        <v>6140</v>
       </c>
       <c r="B42" t="s">
         <v>50</v>
@@ -3046,7 +3156,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>7030</v>
+        <v>6150</v>
       </c>
       <c r="B43" t="s">
         <v>51</v>
@@ -3057,7 +3167,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>7110</v>
+        <v>7010</v>
       </c>
       <c r="B44" t="s">
         <v>52</v>
@@ -3068,7 +3178,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>7120</v>
+        <v>7020</v>
       </c>
       <c r="B45" t="s">
         <v>53</v>
@@ -3079,7 +3189,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>7130</v>
+        <v>7030</v>
       </c>
       <c r="B46" t="s">
         <v>54</v>
@@ -3090,10 +3200,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>8010</v>
+        <v>7040</v>
       </c>
       <c r="B47" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
         <v>10</v>
@@ -3101,10 +3211,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>8020</v>
+        <v>7110</v>
       </c>
       <c r="B48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C48" t="s">
         <v>10</v>
@@ -3112,10 +3222,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>8110</v>
+        <v>7120</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C49" t="s">
         <v>10</v>
@@ -3123,10 +3233,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>8120</v>
+        <v>7130</v>
       </c>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C50" t="s">
         <v>10</v>
@@ -3134,10 +3244,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>8130</v>
+        <v>8010</v>
       </c>
       <c r="B51" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
@@ -3145,10 +3255,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>9010</v>
+        <v>8020</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
         <v>10</v>
@@ -3156,10 +3266,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>9020</v>
+        <v>8110</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
         <v>10</v>
@@ -3167,10 +3277,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>9110</v>
+        <v>8120</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C54" t="s">
         <v>10</v>
@@ -3178,10 +3288,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>9120</v>
+        <v>8130</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C55" t="s">
         <v>10</v>
@@ -3189,12 +3299,56 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
+        <v>9010</v>
+      </c>
+      <c r="B56" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>9020</v>
+      </c>
+      <c r="B57" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>9110</v>
+      </c>
+      <c r="B58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>9120</v>
+      </c>
+      <c r="B59" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
         <v>9130</v>
       </c>
-      <c r="B56" t="s">
-        <v>63</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="B60" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3207,7 +3361,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="15.6363636363636" customWidth="1"/>
@@ -3224,10 +3378,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3235,10 +3389,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3246,10 +3400,10 @@
         <v>1012</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3257,10 +3411,10 @@
         <v>1020</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3268,10 +3422,10 @@
         <v>1030</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3279,10 +3433,10 @@
         <v>1031</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3290,10 +3444,10 @@
         <v>1040</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3301,10 +3455,10 @@
         <v>1050</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3312,10 +3466,10 @@
         <v>1060</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3323,131 +3477,142 @@
         <v>1070</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>2010</v>
+        <v>1080</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>7020</v>
+        <v>3020</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>7040</v>
+        <v>7020</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>7050</v>
+        <v>7040</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>7060</v>
+        <v>7050</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>7080</v>
+        <v>7060</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>8010</v>
+        <v>7080</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
+        <v>8020</v>
+      </c>
+      <c r="B22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
         <v>8030</v>
       </c>
-      <c r="B22" t="s">
-        <v>104</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
+      <c r="B23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410"/>
+    <workbookView windowWidth="19200" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="110">
   <si>
     <t>Id</t>
   </si>
@@ -153,10 +153,16 @@
     <t>与ダメージ累計が5000を超える</t>
   </si>
   <si>
-    <t>エインフェリアを1人転送する</t>
-  </si>
-  <si>
-    <t>Rank6の重要課題を全て達成する</t>
+    <t>いずれかのキャラをクラスチェンジする</t>
+  </si>
+  <si>
+    <t>暗黒の塔のボスを撃破する</t>
+  </si>
+  <si>
+    <t>仲間の封印魔法を8つ以上解放する</t>
+  </si>
+  <si>
+    <t>Rank7の重要課題を全て達成する</t>
   </si>
   <si>
     <t>累計15回以上出撃する</t>
@@ -174,16 +180,10 @@
     <t>与ダメージ累計が7500を超える</t>
   </si>
   <si>
-    <t>いずれかのキャラをクラスチェンジする</t>
-  </si>
-  <si>
-    <t>暗黒の塔のボスを撃破する</t>
-  </si>
-  <si>
-    <t>仲間の封印魔法を8つ以上解放する</t>
-  </si>
-  <si>
-    <t>Rank7の重要課題を全て達成する</t>
+    <t>天空城のボスを撃破する</t>
+  </si>
+  <si>
+    <t>Rank8の重要課題を全て達成する</t>
   </si>
   <si>
     <t>3人以上のキャラLvを25以上にする</t>
@@ -195,10 +195,7 @@
     <t>バトルで交代を5回以上使用する</t>
   </si>
   <si>
-    <t>天空城のボスを撃破する</t>
-  </si>
-  <si>
-    <t>Rank8の重要課題を全て達成する</t>
+    <t>Rank9の重要課題を全て達成する</t>
   </si>
   <si>
     <t>5人以上のキャラLvを25以上にする</t>
@@ -208,9 +205,6 @@
   </si>
   <si>
     <t>3人以上のキャラをクラスチェンジする</t>
-  </si>
-  <si>
-    <t>Rank9の重要課題を全て達成する</t>
   </si>
   <si>
     <t>5人以上のキャラLvを30以上にする</t>
@@ -359,10 +353,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -374,9 +368,39 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -387,18 +411,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -411,15 +428,29 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -442,26 +473,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -482,36 +497,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -526,7 +520,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -538,7 +562,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,13 +574,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -568,7 +604,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,7 +628,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,25 +664,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -628,85 +688,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -721,16 +715,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -746,6 +740,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -770,15 +782,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -795,25 +798,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -825,145 +819,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -980,12 +974,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1290,7 +1284,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9.54545454545454"/>
@@ -1431,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1592,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1776,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>15050</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1845,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1914,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>14020</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1937,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>14020</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1960,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2132,10 +2126,10 @@
         <v>10</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37">
-        <v>7060</v>
+        <v>1070</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -2144,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>40020</v>
+        <v>14310</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2155,70 +2149,70 @@
         <v>10</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>20010</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>6110</v>
+        <v>6030</v>
       </c>
       <c r="B39">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39">
-        <v>1010</v>
+        <v>1080</v>
       </c>
       <c r="E39">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>6120</v>
+        <v>6040</v>
       </c>
       <c r="B40">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D40">
-        <v>1020</v>
+        <v>10</v>
       </c>
       <c r="E40">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>6130</v>
+        <v>6110</v>
       </c>
       <c r="B41">
         <v>20</v>
@@ -2227,13 +2221,13 @@
         <v>6</v>
       </c>
       <c r="D41">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="E41">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G41">
         <v>2</v>
@@ -2241,7 +2235,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>6140</v>
+        <v>6120</v>
       </c>
       <c r="B42">
         <v>20</v>
@@ -2250,10 +2244,10 @@
         <v>6</v>
       </c>
       <c r="D42">
-        <v>1050</v>
+        <v>1020</v>
       </c>
       <c r="E42">
-        <v>1500</v>
+        <v>75</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2264,7 +2258,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>6150</v>
+        <v>6130</v>
       </c>
       <c r="B43">
         <v>20</v>
@@ -2273,13 +2267,13 @@
         <v>6</v>
       </c>
       <c r="D43">
-        <v>1060</v>
+        <v>1030</v>
       </c>
       <c r="E43">
-        <v>7500</v>
+        <v>20</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -2287,53 +2281,53 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>7010</v>
+        <v>6140</v>
       </c>
       <c r="B44">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D44">
-        <v>1070</v>
+        <v>1050</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44">
-        <v>14310</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>7020</v>
+        <v>6150</v>
       </c>
       <c r="B45">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D45">
-        <v>2010</v>
+        <v>1060</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>7500</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="G45">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>7030</v>
+        <v>7010</v>
       </c>
       <c r="B46">
         <v>10</v>
@@ -2342,21 +2336,21 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>1080</v>
+        <v>2010</v>
       </c>
       <c r="E46">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F46">
         <v>0</v>
       </c>
       <c r="G46">
-        <v>1100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>7040</v>
+        <v>7020</v>
       </c>
       <c r="B47">
         <v>10</v>
@@ -2454,19 +2448,19 @@
         <v>10</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D51">
-        <v>2010</v>
+        <v>1012</v>
       </c>
       <c r="E51">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51">
-        <v>25</v>
+        <v>15050</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2477,7 +2471,7 @@
         <v>10</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D52">
         <v>10</v>
@@ -2563,53 +2557,53 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>9010</v>
+        <v>9110</v>
       </c>
       <c r="B56">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C56">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D56">
-        <v>1012</v>
+        <v>1031</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G56">
-        <v>15050</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>9020</v>
+        <v>9120</v>
       </c>
       <c r="B57">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C57">
         <v>9</v>
       </c>
       <c r="D57">
-        <v>10</v>
+        <v>7060</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="G57">
-        <v>20010</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>9110</v>
+        <v>9130</v>
       </c>
       <c r="B58">
         <v>20</v>
@@ -2618,61 +2612,15 @@
         <v>9</v>
       </c>
       <c r="D58">
-        <v>1031</v>
+        <v>1070</v>
       </c>
       <c r="E58">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F58">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G58">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59">
-        <v>9120</v>
-      </c>
-      <c r="B59">
-        <v>20</v>
-      </c>
-      <c r="C59">
-        <v>9</v>
-      </c>
-      <c r="D59">
-        <v>7060</v>
-      </c>
-      <c r="E59">
-        <v>3</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60">
-        <v>9130</v>
-      </c>
-      <c r="B60">
-        <v>20</v>
-      </c>
-      <c r="C60">
-        <v>9</v>
-      </c>
-      <c r="D60">
-        <v>1070</v>
-      </c>
-      <c r="E60">
-        <v>5</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60">
         <v>2</v>
       </c>
     </row>
@@ -2685,7 +2633,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
@@ -3112,7 +3060,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>6110</v>
+        <v>6030</v>
       </c>
       <c r="B39" t="s">
         <v>47</v>
@@ -3123,7 +3071,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>6120</v>
+        <v>6040</v>
       </c>
       <c r="B40" t="s">
         <v>48</v>
@@ -3134,7 +3082,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>6130</v>
+        <v>6110</v>
       </c>
       <c r="B41" t="s">
         <v>49</v>
@@ -3145,7 +3093,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>6140</v>
+        <v>6120</v>
       </c>
       <c r="B42" t="s">
         <v>50</v>
@@ -3156,7 +3104,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>6150</v>
+        <v>6130</v>
       </c>
       <c r="B43" t="s">
         <v>51</v>
@@ -3167,7 +3115,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>7010</v>
+        <v>6140</v>
       </c>
       <c r="B44" t="s">
         <v>52</v>
@@ -3178,7 +3126,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>7020</v>
+        <v>6150</v>
       </c>
       <c r="B45" t="s">
         <v>53</v>
@@ -3189,7 +3137,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>7030</v>
+        <v>7010</v>
       </c>
       <c r="B46" t="s">
         <v>54</v>
@@ -3200,7 +3148,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>7040</v>
+        <v>7020</v>
       </c>
       <c r="B47" t="s">
         <v>55</v>
@@ -3247,7 +3195,7 @@
         <v>8010</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
@@ -3258,7 +3206,7 @@
         <v>8020</v>
       </c>
       <c r="B52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C52" t="s">
         <v>10</v>
@@ -3269,7 +3217,7 @@
         <v>8110</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C53" t="s">
         <v>10</v>
@@ -3280,7 +3228,7 @@
         <v>8120</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C54" t="s">
         <v>10</v>
@@ -3291,7 +3239,7 @@
         <v>8130</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C55" t="s">
         <v>10</v>
@@ -3299,10 +3247,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>9010</v>
+        <v>9110</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C56" t="s">
         <v>10</v>
@@ -3310,7 +3258,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>9020</v>
+        <v>9120</v>
       </c>
       <c r="B57" t="s">
         <v>64</v>
@@ -3321,34 +3269,12 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>9110</v>
+        <v>9130</v>
       </c>
       <c r="B58" t="s">
         <v>65</v>
       </c>
       <c r="C58" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59">
-        <v>9120</v>
-      </c>
-      <c r="B59" t="s">
-        <v>66</v>
-      </c>
-      <c r="C59" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60">
-        <v>9130</v>
-      </c>
-      <c r="B60" t="s">
-        <v>67</v>
-      </c>
-      <c r="C60" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3378,10 +3304,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3389,10 +3315,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3400,10 +3326,10 @@
         <v>1012</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3411,10 +3337,10 @@
         <v>1020</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3422,10 +3348,10 @@
         <v>1030</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3433,10 +3359,10 @@
         <v>1031</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3444,10 +3370,10 @@
         <v>1040</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3455,10 +3381,10 @@
         <v>1050</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3466,10 +3392,10 @@
         <v>1060</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3477,10 +3403,10 @@
         <v>1070</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3488,10 +3414,10 @@
         <v>1080</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3499,10 +3425,10 @@
         <v>2010</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3510,10 +3436,10 @@
         <v>3010</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3521,10 +3447,10 @@
         <v>3020</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3532,10 +3458,10 @@
         <v>7020</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3543,10 +3469,10 @@
         <v>7040</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3554,10 +3480,10 @@
         <v>7050</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3565,10 +3491,10 @@
         <v>7060</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3576,10 +3502,10 @@
         <v>7080</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3587,10 +3513,10 @@
         <v>8010</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3598,10 +3524,10 @@
         <v>8020</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3609,10 +3535,10 @@
         <v>8030</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="107">
   <si>
     <t>Id</t>
   </si>
@@ -75,7 +75,7 @@
     <t>いずれかのキャラLvを3以上にする</t>
   </si>
   <si>
-    <t>評価値を3%以上にする</t>
+    <t>評価値を100以上にする</t>
   </si>
   <si>
     <t>与ダメージ累計が200を超える</t>
@@ -99,9 +99,6 @@
     <t>いずれかのキャラLvを7以上にする</t>
   </si>
   <si>
-    <t>評価値を5%以上にする</t>
-  </si>
-  <si>
     <t>与ダメージ累計が1500を超える</t>
   </si>
   <si>
@@ -147,9 +144,6 @@
     <t>いずれかのキャラLvを15以上にする</t>
   </si>
   <si>
-    <t>評価値を10%以上にする</t>
-  </si>
-  <si>
     <t>与ダメージ累計が5000を超える</t>
   </si>
   <si>
@@ -172,9 +166,6 @@
   </si>
   <si>
     <t>いずれかのキャラLvを20以上にする</t>
-  </si>
-  <si>
-    <t>評価値を15%以上にする</t>
   </si>
   <si>
     <t>与ダメージ累計が7500を超える</t>
@@ -353,10 +344,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -367,8 +358,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -381,9 +380,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -396,16 +410,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -419,28 +448,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -448,9 +464,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -464,48 +495,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -526,25 +517,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -556,7 +541,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,19 +559,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,7 +589,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -610,79 +667,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -700,7 +685,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -747,8 +738,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -756,18 +762,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -797,17 +792,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -819,22 +810,22 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -843,121 +834,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1425,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1534,7 +1525,7 @@
         <v>1050</v>
       </c>
       <c r="E11">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1586,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1718,7 +1709,7 @@
         <v>1050</v>
       </c>
       <c r="E19">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1770,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1839,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1954,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2086,7 +2077,7 @@
         <v>1050</v>
       </c>
       <c r="E35">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2161,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2293,7 +2284,7 @@
         <v>1050</v>
       </c>
       <c r="E44">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2345,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2843,7 +2834,7 @@
         <v>3040</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -2854,7 +2845,7 @@
         <v>3050</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -2865,7 +2856,7 @@
         <v>3060</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -2876,7 +2867,7 @@
         <v>3070</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -2887,7 +2878,7 @@
         <v>3080</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -2898,7 +2889,7 @@
         <v>4010</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
@@ -2909,7 +2900,7 @@
         <v>4020</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
@@ -2920,7 +2911,7 @@
         <v>5010</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
@@ -2931,7 +2922,7 @@
         <v>5020</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
@@ -2942,7 +2933,7 @@
         <v>5030</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -2953,7 +2944,7 @@
         <v>5040</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
@@ -2964,7 +2955,7 @@
         <v>5050</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
@@ -2975,7 +2966,7 @@
         <v>5060</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31" t="s">
         <v>10</v>
@@ -2986,7 +2977,7 @@
         <v>5110</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
         <v>10</v>
@@ -2997,7 +2988,7 @@
         <v>5120</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
         <v>10</v>
@@ -3008,7 +2999,7 @@
         <v>5130</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
@@ -3019,7 +3010,7 @@
         <v>5140</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s">
         <v>10</v>
@@ -3030,7 +3021,7 @@
         <v>5150</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
@@ -3041,7 +3032,7 @@
         <v>6010</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
         <v>10</v>
@@ -3052,7 +3043,7 @@
         <v>6020</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
         <v>10</v>
@@ -3063,7 +3054,7 @@
         <v>6030</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C39" t="s">
         <v>10</v>
@@ -3074,7 +3065,7 @@
         <v>6040</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
         <v>10</v>
@@ -3085,7 +3076,7 @@
         <v>6110</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C41" t="s">
         <v>10</v>
@@ -3096,7 +3087,7 @@
         <v>6120</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
@@ -3107,7 +3098,7 @@
         <v>6130</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C43" t="s">
         <v>10</v>
@@ -3118,7 +3109,7 @@
         <v>6140</v>
       </c>
       <c r="B44" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="C44" t="s">
         <v>10</v>
@@ -3129,7 +3120,7 @@
         <v>6150</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C45" t="s">
         <v>10</v>
@@ -3140,7 +3131,7 @@
         <v>7010</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C46" t="s">
         <v>10</v>
@@ -3151,7 +3142,7 @@
         <v>7020</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C47" t="s">
         <v>10</v>
@@ -3162,7 +3153,7 @@
         <v>7110</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
         <v>10</v>
@@ -3173,7 +3164,7 @@
         <v>7120</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C49" t="s">
         <v>10</v>
@@ -3184,7 +3175,7 @@
         <v>7130</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C50" t="s">
         <v>10</v>
@@ -3195,7 +3186,7 @@
         <v>8010</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
@@ -3206,7 +3197,7 @@
         <v>8020</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
         <v>10</v>
@@ -3217,7 +3208,7 @@
         <v>8110</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C53" t="s">
         <v>10</v>
@@ -3228,7 +3219,7 @@
         <v>8120</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
         <v>10</v>
@@ -3239,7 +3230,7 @@
         <v>8130</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C55" t="s">
         <v>10</v>
@@ -3250,7 +3241,7 @@
         <v>9110</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C56" t="s">
         <v>10</v>
@@ -3261,7 +3252,7 @@
         <v>9120</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C57" t="s">
         <v>10</v>
@@ -3272,7 +3263,7 @@
         <v>9130</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C58" t="s">
         <v>10</v>
@@ -3304,10 +3295,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3315,10 +3306,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3326,10 +3317,10 @@
         <v>1012</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3337,10 +3328,10 @@
         <v>1020</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3348,10 +3339,10 @@
         <v>1030</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3359,10 +3350,10 @@
         <v>1031</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3370,10 +3361,10 @@
         <v>1040</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3381,10 +3372,10 @@
         <v>1050</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3392,10 +3383,10 @@
         <v>1060</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3403,10 +3394,10 @@
         <v>1070</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3414,10 +3405,10 @@
         <v>1080</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3425,10 +3416,10 @@
         <v>2010</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3436,10 +3427,10 @@
         <v>3010</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3447,10 +3438,10 @@
         <v>3020</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3458,10 +3449,10 @@
         <v>7020</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3469,10 +3460,10 @@
         <v>7040</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3480,10 +3471,10 @@
         <v>7050</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3491,10 +3482,10 @@
         <v>7060</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3502,10 +3493,10 @@
         <v>7080</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3513,10 +3504,10 @@
         <v>8010</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3524,10 +3515,10 @@
         <v>8020</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3535,10 +3526,10 @@
         <v>8030</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -345,8 +345,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -358,11 +358,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -380,16 +395,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -410,8 +426,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -424,11 +455,27 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -441,55 +488,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -517,7 +517,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -529,31 +631,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -565,133 +691,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -737,9 +737,38 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -759,24 +788,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -791,17 +802,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -810,22 +810,22 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -834,121 +834,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>14010</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>14010</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:7">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -344,10 +344,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -355,6 +355,28 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -367,7 +389,61 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -381,46 +457,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -448,37 +487,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -487,16 +495,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -511,7 +511,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,7 +607,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,25 +625,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -565,19 +661,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,109 +691,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -702,6 +702,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -716,32 +727,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -764,11 +749,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -787,21 +802,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -810,145 +810,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>10010</v>
+        <v>31010</v>
       </c>
     </row>
     <row r="5" spans="1:7">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -57,10 +57,10 @@
     <t>編成コマンドで仲間を編成する</t>
   </si>
   <si>
-    <t>献上コマンドで魔法を入手する</t>
-  </si>
-  <si>
-    <t>仲間の魔法装備を変更する</t>
+    <t>献上コマンドで装備を入手する</t>
+  </si>
+  <si>
+    <t>仲間の装備を変更する</t>
   </si>
   <si>
     <t>Rank1の重要課題を全て達成する</t>
@@ -359,6 +359,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -366,45 +373,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -413,6 +382,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -436,7 +412,45 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -451,37 +465,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -489,16 +473,32 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -511,19 +511,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,19 +535,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,13 +559,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,7 +583,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -595,13 +601,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -619,79 +673,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,11 +707,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -735,30 +742,21 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -766,9 +764,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -788,16 +788,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -810,7 +810,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -819,136 +819,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>31010</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="5" spans="1:7">

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="110">
   <si>
     <t>Id</t>
   </si>
@@ -75,7 +75,7 @@
     <t>いずれかのキャラLvを3以上にする</t>
   </si>
   <si>
-    <t>評価値を100以上にする</t>
+    <t>評価値を累計100以上獲得する</t>
   </si>
   <si>
     <t>与ダメージ累計が200を超える</t>
@@ -99,6 +99,9 @@
     <t>いずれかのキャラLvを7以上にする</t>
   </si>
   <si>
+    <t>評価値を累計500以上獲得する</t>
+  </si>
+  <si>
     <t>与ダメージ累計が1500を超える</t>
   </si>
   <si>
@@ -144,6 +147,9 @@
     <t>いずれかのキャラLvを15以上にする</t>
   </si>
   <si>
+    <t>評価値を累計1500以上獲得する</t>
+  </si>
+  <si>
     <t>与ダメージ累計が5000を超える</t>
   </si>
   <si>
@@ -166,6 +172,9 @@
   </si>
   <si>
     <t>いずれかのキャラLvを20以上にする</t>
+  </si>
+  <si>
+    <t>評価値を累計3000以上獲得する</t>
   </si>
   <si>
     <t>与ダメージ累計が7500を超える</t>
@@ -344,10 +353,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -373,10 +382,18 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -388,17 +405,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -412,14 +442,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -434,55 +457,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -495,10 +473,41 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -511,7 +520,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,13 +544,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -547,103 +688,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,43 +700,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,9 +716,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -738,11 +764,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -764,41 +805,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -810,145 +819,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1709,7 +1718,7 @@
         <v>1050</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -2077,7 +2086,7 @@
         <v>1050</v>
       </c>
       <c r="E35">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2284,7 +2293,7 @@
         <v>1050</v>
       </c>
       <c r="E44">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2834,7 +2843,7 @@
         <v>3040</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -2845,7 +2854,7 @@
         <v>3050</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -2856,7 +2865,7 @@
         <v>3060</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -2867,7 +2876,7 @@
         <v>3070</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -2878,7 +2887,7 @@
         <v>3080</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -2889,7 +2898,7 @@
         <v>4010</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
@@ -2900,7 +2909,7 @@
         <v>4020</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
@@ -2911,7 +2920,7 @@
         <v>5010</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
@@ -2922,7 +2931,7 @@
         <v>5020</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
@@ -2933,7 +2942,7 @@
         <v>5030</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -2944,7 +2953,7 @@
         <v>5040</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
@@ -2955,7 +2964,7 @@
         <v>5050</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
@@ -2966,7 +2975,7 @@
         <v>5060</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
         <v>10</v>
@@ -2977,7 +2986,7 @@
         <v>5110</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
         <v>10</v>
@@ -2988,7 +2997,7 @@
         <v>5120</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
         <v>10</v>
@@ -2999,7 +3008,7 @@
         <v>5130</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
@@ -3010,7 +3019,7 @@
         <v>5140</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
         <v>10</v>
@@ -3021,7 +3030,7 @@
         <v>5150</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
@@ -3032,7 +3041,7 @@
         <v>6010</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C37" t="s">
         <v>10</v>
@@ -3043,7 +3052,7 @@
         <v>6020</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C38" t="s">
         <v>10</v>
@@ -3054,7 +3063,7 @@
         <v>6030</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
         <v>10</v>
@@ -3065,7 +3074,7 @@
         <v>6040</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C40" t="s">
         <v>10</v>
@@ -3076,7 +3085,7 @@
         <v>6110</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
         <v>10</v>
@@ -3087,7 +3096,7 @@
         <v>6120</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
@@ -3098,7 +3107,7 @@
         <v>6130</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
         <v>10</v>
@@ -3109,7 +3118,7 @@
         <v>6140</v>
       </c>
       <c r="B44" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C44" t="s">
         <v>10</v>
@@ -3120,7 +3129,7 @@
         <v>6150</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
         <v>10</v>
@@ -3131,7 +3140,7 @@
         <v>7010</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
         <v>10</v>
@@ -3142,7 +3151,7 @@
         <v>7020</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
         <v>10</v>
@@ -3153,7 +3162,7 @@
         <v>7110</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C48" t="s">
         <v>10</v>
@@ -3164,7 +3173,7 @@
         <v>7120</v>
       </c>
       <c r="B49" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C49" t="s">
         <v>10</v>
@@ -3175,7 +3184,7 @@
         <v>7130</v>
       </c>
       <c r="B50" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C50" t="s">
         <v>10</v>
@@ -3186,7 +3195,7 @@
         <v>8010</v>
       </c>
       <c r="B51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
@@ -3197,7 +3206,7 @@
         <v>8020</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C52" t="s">
         <v>10</v>
@@ -3208,7 +3217,7 @@
         <v>8110</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C53" t="s">
         <v>10</v>
@@ -3219,7 +3228,7 @@
         <v>8120</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C54" t="s">
         <v>10</v>
@@ -3230,7 +3239,7 @@
         <v>8130</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C55" t="s">
         <v>10</v>
@@ -3241,7 +3250,7 @@
         <v>9110</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C56" t="s">
         <v>10</v>
@@ -3252,7 +3261,7 @@
         <v>9120</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C57" t="s">
         <v>10</v>
@@ -3263,7 +3272,7 @@
         <v>9130</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C58" t="s">
         <v>10</v>
@@ -3295,10 +3304,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3306,10 +3315,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3317,10 +3326,10 @@
         <v>1012</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3328,10 +3337,10 @@
         <v>1020</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3339,10 +3348,10 @@
         <v>1030</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3350,10 +3359,10 @@
         <v>1031</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3361,10 +3370,10 @@
         <v>1040</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3372,10 +3381,10 @@
         <v>1050</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3383,10 +3392,10 @@
         <v>1060</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3394,10 +3403,10 @@
         <v>1070</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3405,10 +3414,10 @@
         <v>1080</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3416,10 +3425,10 @@
         <v>2010</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3427,10 +3436,10 @@
         <v>3010</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3438,10 +3447,10 @@
         <v>3020</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3449,10 +3458,10 @@
         <v>7020</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3460,10 +3469,10 @@
         <v>7040</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3471,10 +3480,10 @@
         <v>7050</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3482,10 +3491,10 @@
         <v>7060</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3493,10 +3502,10 @@
         <v>7080</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3504,10 +3513,10 @@
         <v>8010</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3515,10 +3524,10 @@
         <v>8020</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3526,10 +3535,10 @@
         <v>8030</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="113">
   <si>
     <t>Id</t>
   </si>
@@ -51,15 +51,18 @@
     <t>""</t>
   </si>
   <si>
+    <t>編成コマンドで仲間を編成する</t>
+  </si>
+  <si>
     <t>アイテムを使用していずれかのキャラのLvを上げる</t>
   </si>
   <si>
-    <t>編成コマンドで仲間を編成する</t>
-  </si>
-  <si>
     <t>献上コマンドで装備を入手する</t>
   </si>
   <si>
+    <t>取引コマンドでアイテムか装備を入手する</t>
+  </si>
+  <si>
     <t>仲間の装備を変更する</t>
   </si>
   <si>
@@ -322,6 +325,12 @@
   </si>
   <si>
     <t>転送回数</t>
+  </si>
+  <si>
+    <t>TradeCommandCount</t>
+  </si>
+  <si>
+    <t>取引回数</t>
   </si>
   <si>
     <t>StatusSkillChangeCount</t>
@@ -354,9 +363,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -364,6 +373,22 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -383,6 +408,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -390,8 +431,61 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -405,94 +499,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -520,13 +529,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -538,7 +565,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,37 +577,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -592,13 +607,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -622,37 +637,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -664,7 +649,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,19 +673,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -700,7 +685,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -711,17 +720,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -740,11 +738,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -760,6 +764,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -781,24 +794,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -807,7 +807,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -819,145 +828,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1284,7 +1293,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9.54545454545454"/>
@@ -1347,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1040</v>
+        <v>7020</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1356,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>15050</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1370,7 +1379,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>7020</v>
+        <v>1040</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1379,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>10010</v>
+        <v>15050</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1402,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1416,7 +1425,7 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>7080</v>
+        <v>7070</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1425,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>14010</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1439,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>7080</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1448,21 +1457,21 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>20010</v>
+        <v>14010</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>2010</v>
+        <v>1070</v>
       </c>
       <c r="B8">
         <v>10</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1471,12 +1480,12 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>14010</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -1485,21 +1494,21 @@
         <v>2</v>
       </c>
       <c r="D9">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>10020</v>
+        <v>14010</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -1508,21 +1517,21 @@
         <v>2</v>
       </c>
       <c r="D10">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>10030</v>
+        <v>10020</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -1531,21 +1540,21 @@
         <v>2</v>
       </c>
       <c r="D11">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G11">
-        <v>10040</v>
+        <v>10030</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -1554,21 +1563,21 @@
         <v>2</v>
       </c>
       <c r="D12">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="E12">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>10050</v>
+        <v>10040</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="B13">
         <v>10</v>
@@ -1577,21 +1586,21 @@
         <v>2</v>
       </c>
       <c r="D13">
-        <v>2010</v>
+        <v>1060</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>50</v>
+        <v>10050</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="B14">
         <v>10</v>
@@ -1600,7 +1609,7 @@
         <v>2</v>
       </c>
       <c r="D14">
-        <v>1080</v>
+        <v>2010</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -1609,12 +1618,12 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>1100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="B15">
         <v>10</v>
@@ -1623,7 +1632,7 @@
         <v>2</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>1080</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -1632,35 +1641,35 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>20010</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>3010</v>
+        <v>2080</v>
       </c>
       <c r="B16">
         <v>10</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>10010</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B17">
         <v>10</v>
@@ -1669,21 +1678,21 @@
         <v>3</v>
       </c>
       <c r="D17">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>10020</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B18">
         <v>10</v>
@@ -1692,21 +1701,21 @@
         <v>3</v>
       </c>
       <c r="D18">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="E18">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>10030</v>
+        <v>10020</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B19">
         <v>10</v>
@@ -1715,21 +1724,21 @@
         <v>3</v>
       </c>
       <c r="D19">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="E19">
-        <v>500</v>
+        <v>7</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G19">
-        <v>10040</v>
+        <v>10030</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>3050</v>
+        <v>3040</v>
       </c>
       <c r="B20">
         <v>10</v>
@@ -1738,21 +1747,21 @@
         <v>3</v>
       </c>
       <c r="D20">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="E20">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>10050</v>
+        <v>10040</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>3060</v>
+        <v>3050</v>
       </c>
       <c r="B21">
         <v>10</v>
@@ -1761,21 +1770,21 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>2010</v>
+        <v>1060</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>1500</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>20</v>
+        <v>10050</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>3070</v>
+        <v>3060</v>
       </c>
       <c r="B22">
         <v>10</v>
@@ -1784,21 +1793,21 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>1080</v>
+        <v>2010</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>1100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>3080</v>
+        <v>3070</v>
       </c>
       <c r="B23">
         <v>10</v>
@@ -1807,44 +1816,44 @@
         <v>3</v>
       </c>
       <c r="D23">
-        <v>10</v>
+        <v>1080</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>20010</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>4010</v>
+        <v>3080</v>
       </c>
       <c r="B24">
         <v>10</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24">
-        <v>1012</v>
+        <v>10</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>20</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B25">
         <v>10</v>
@@ -1853,44 +1862,44 @@
         <v>4</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>1012</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>20010</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>5010</v>
+        <v>4020</v>
       </c>
       <c r="B26">
         <v>10</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>1031</v>
+        <v>10</v>
       </c>
       <c r="E26">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>15060</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B27">
         <v>10</v>
@@ -1899,21 +1908,21 @@
         <v>5</v>
       </c>
       <c r="D27">
-        <v>3010</v>
+        <v>1031</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>14020</v>
+        <v>15060</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="B28">
         <v>10</v>
@@ -1922,7 +1931,7 @@
         <v>5</v>
       </c>
       <c r="D28">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -1936,7 +1945,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="B29">
         <v>10</v>
@@ -1945,21 +1954,21 @@
         <v>5</v>
       </c>
       <c r="D29">
-        <v>2010</v>
+        <v>3020</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>20</v>
+        <v>14020</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="B30">
         <v>10</v>
@@ -1968,21 +1977,21 @@
         <v>5</v>
       </c>
       <c r="D30">
-        <v>1080</v>
+        <v>2010</v>
       </c>
       <c r="E30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>1100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="B31">
         <v>10</v>
@@ -1991,44 +2000,44 @@
         <v>5</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>1080</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>20010</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>5110</v>
+        <v>5060</v>
       </c>
       <c r="B32">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C32">
         <v>5</v>
       </c>
       <c r="D32">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>5120</v>
+        <v>5110</v>
       </c>
       <c r="B33">
         <v>20</v>
@@ -2037,10 +2046,10 @@
         <v>5</v>
       </c>
       <c r="D33">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="E33">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2051,7 +2060,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>5130</v>
+        <v>5120</v>
       </c>
       <c r="B34">
         <v>20</v>
@@ -2060,13 +2069,13 @@
         <v>5</v>
       </c>
       <c r="D34">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="E34">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -2074,7 +2083,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>5140</v>
+        <v>5130</v>
       </c>
       <c r="B35">
         <v>20</v>
@@ -2083,13 +2092,13 @@
         <v>5</v>
       </c>
       <c r="D35">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="E35">
-        <v>1500</v>
+        <v>15</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -2097,7 +2106,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>5150</v>
+        <v>5140</v>
       </c>
       <c r="B36">
         <v>20</v>
@@ -2106,10 +2115,10 @@
         <v>5</v>
       </c>
       <c r="D36">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="E36">
-        <v>5000</v>
+        <v>1500</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2120,30 +2129,30 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>6010</v>
+        <v>5150</v>
       </c>
       <c r="B37">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D37">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="F37">
         <v>0</v>
       </c>
       <c r="G37">
-        <v>14310</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="B38">
         <v>10</v>
@@ -2152,21 +2161,21 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>2010</v>
+        <v>1070</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>20</v>
+        <v>14310</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="B39">
         <v>10</v>
@@ -2175,21 +2184,21 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>1080</v>
+        <v>2010</v>
       </c>
       <c r="E39">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39">
-        <v>1100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>6040</v>
+        <v>6030</v>
       </c>
       <c r="B40">
         <v>10</v>
@@ -2198,44 +2207,44 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>1080</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40">
-        <v>20010</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>6110</v>
+        <v>6040</v>
       </c>
       <c r="B41">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="E41">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>6120</v>
+        <v>6110</v>
       </c>
       <c r="B42">
         <v>20</v>
@@ -2244,10 +2253,10 @@
         <v>6</v>
       </c>
       <c r="D42">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="E42">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2258,7 +2267,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>6130</v>
+        <v>6120</v>
       </c>
       <c r="B43">
         <v>20</v>
@@ -2267,13 +2276,13 @@
         <v>6</v>
       </c>
       <c r="D43">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="E43">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="F43">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -2281,7 +2290,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>6140</v>
+        <v>6130</v>
       </c>
       <c r="B44">
         <v>20</v>
@@ -2290,13 +2299,13 @@
         <v>6</v>
       </c>
       <c r="D44">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="E44">
-        <v>3000</v>
+        <v>20</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -2304,7 +2313,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>6150</v>
+        <v>6140</v>
       </c>
       <c r="B45">
         <v>20</v>
@@ -2313,10 +2322,10 @@
         <v>6</v>
       </c>
       <c r="D45">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="E45">
-        <v>7500</v>
+        <v>3000</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2327,30 +2336,30 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>7010</v>
+        <v>6150</v>
       </c>
       <c r="B46">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D46">
-        <v>2010</v>
+        <v>1060</v>
       </c>
       <c r="E46">
-        <v>6</v>
+        <v>7500</v>
       </c>
       <c r="F46">
         <v>0</v>
       </c>
       <c r="G46">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>7020</v>
+        <v>7010</v>
       </c>
       <c r="B47">
         <v>10</v>
@@ -2359,44 +2368,44 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47">
-        <v>20010</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>7110</v>
+        <v>7020</v>
       </c>
       <c r="B48">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C48">
         <v>7</v>
       </c>
       <c r="D48">
-        <v>1031</v>
+        <v>10</v>
       </c>
       <c r="E48">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>7120</v>
+        <v>7110</v>
       </c>
       <c r="B49">
         <v>20</v>
@@ -2405,13 +2414,13 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>3010</v>
+        <v>1031</v>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G49">
         <v>2</v>
@@ -2419,7 +2428,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>7130</v>
+        <v>7120</v>
       </c>
       <c r="B50">
         <v>20</v>
@@ -2428,7 +2437,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="E50">
         <v>5</v>
@@ -2442,39 +2451,39 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>8010</v>
+        <v>7130</v>
       </c>
       <c r="B51">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C51">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D51">
-        <v>1012</v>
+        <v>3020</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51">
-        <v>15050</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="B52">
         <v>10</v>
       </c>
       <c r="C52">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D52">
-        <v>10</v>
+        <v>1012</v>
       </c>
       <c r="E52">
         <v>2</v>
@@ -2483,35 +2492,35 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>20010</v>
+        <v>15050</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>8110</v>
+        <v>8020</v>
       </c>
       <c r="B53">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C53">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D53">
-        <v>1031</v>
+        <v>10</v>
       </c>
       <c r="E53">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>8120</v>
+        <v>8110</v>
       </c>
       <c r="B54">
         <v>20</v>
@@ -2520,13 +2529,13 @@
         <v>8</v>
       </c>
       <c r="D54">
-        <v>7060</v>
+        <v>1031</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -2534,7 +2543,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>8130</v>
+        <v>8120</v>
       </c>
       <c r="B55">
         <v>20</v>
@@ -2543,10 +2552,10 @@
         <v>8</v>
       </c>
       <c r="D55">
-        <v>1070</v>
+        <v>7060</v>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2557,22 +2566,22 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>9110</v>
+        <v>8130</v>
       </c>
       <c r="B56">
         <v>20</v>
       </c>
       <c r="C56">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D56">
-        <v>1031</v>
+        <v>1070</v>
       </c>
       <c r="E56">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F56">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G56">
         <v>2</v>
@@ -2580,7 +2589,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>9120</v>
+        <v>9110</v>
       </c>
       <c r="B57">
         <v>20</v>
@@ -2589,13 +2598,13 @@
         <v>9</v>
       </c>
       <c r="D57">
-        <v>7060</v>
+        <v>1031</v>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G57">
         <v>2</v>
@@ -2603,7 +2612,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>9130</v>
+        <v>9120</v>
       </c>
       <c r="B58">
         <v>20</v>
@@ -2612,15 +2621,38 @@
         <v>9</v>
       </c>
       <c r="D58">
+        <v>7060</v>
+      </c>
+      <c r="E58">
+        <v>3</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>9130</v>
+      </c>
+      <c r="B59">
+        <v>20</v>
+      </c>
+      <c r="C59">
+        <v>9</v>
+      </c>
+      <c r="D59">
         <v>1070</v>
       </c>
-      <c r="E58">
+      <c r="E59">
         <v>5</v>
       </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58">
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
         <v>2</v>
       </c>
     </row>
@@ -2633,7 +2665,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
@@ -2719,7 +2751,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>2010</v>
+        <v>1070</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
@@ -2730,7 +2762,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -2741,7 +2773,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B10" t="s">
         <v>18</v>
@@ -2752,7 +2784,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -2763,7 +2795,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="B12" t="s">
         <v>20</v>
@@ -2774,7 +2806,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="B13" t="s">
         <v>21</v>
@@ -2785,7 +2817,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
@@ -2796,7 +2828,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
@@ -2807,7 +2839,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>3010</v>
+        <v>2080</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
@@ -2818,7 +2850,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B17" t="s">
         <v>25</v>
@@ -2829,7 +2861,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
@@ -2840,7 +2872,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
@@ -2851,7 +2883,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>3050</v>
+        <v>3040</v>
       </c>
       <c r="B20" t="s">
         <v>28</v>
@@ -2862,7 +2894,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>3060</v>
+        <v>3050</v>
       </c>
       <c r="B21" t="s">
         <v>29</v>
@@ -2873,7 +2905,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3070</v>
+        <v>3060</v>
       </c>
       <c r="B22" t="s">
         <v>30</v>
@@ -2884,7 +2916,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>3080</v>
+        <v>3070</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -2895,7 +2927,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>4010</v>
+        <v>3080</v>
       </c>
       <c r="B24" t="s">
         <v>32</v>
@@ -2906,7 +2938,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
@@ -2917,7 +2949,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>5010</v>
+        <v>4020</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -2928,7 +2960,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
@@ -2939,7 +2971,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="B28" t="s">
         <v>36</v>
@@ -2950,7 +2982,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -2961,7 +2993,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="B30" t="s">
         <v>38</v>
@@ -2972,7 +3004,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="B31" t="s">
         <v>39</v>
@@ -2983,7 +3015,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>5110</v>
+        <v>5060</v>
       </c>
       <c r="B32" t="s">
         <v>40</v>
@@ -2994,7 +3026,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>5120</v>
+        <v>5110</v>
       </c>
       <c r="B33" t="s">
         <v>41</v>
@@ -3005,7 +3037,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>5130</v>
+        <v>5120</v>
       </c>
       <c r="B34" t="s">
         <v>42</v>
@@ -3016,7 +3048,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>5140</v>
+        <v>5130</v>
       </c>
       <c r="B35" t="s">
         <v>43</v>
@@ -3027,7 +3059,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>5150</v>
+        <v>5140</v>
       </c>
       <c r="B36" t="s">
         <v>44</v>
@@ -3038,7 +3070,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>6010</v>
+        <v>5150</v>
       </c>
       <c r="B37" t="s">
         <v>45</v>
@@ -3049,7 +3081,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -3060,7 +3092,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="B39" t="s">
         <v>47</v>
@@ -3071,7 +3103,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>6040</v>
+        <v>6030</v>
       </c>
       <c r="B40" t="s">
         <v>48</v>
@@ -3082,7 +3114,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>6110</v>
+        <v>6040</v>
       </c>
       <c r="B41" t="s">
         <v>49</v>
@@ -3093,7 +3125,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>6120</v>
+        <v>6110</v>
       </c>
       <c r="B42" t="s">
         <v>50</v>
@@ -3104,7 +3136,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>6130</v>
+        <v>6120</v>
       </c>
       <c r="B43" t="s">
         <v>51</v>
@@ -3115,7 +3147,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>6140</v>
+        <v>6130</v>
       </c>
       <c r="B44" t="s">
         <v>52</v>
@@ -3126,7 +3158,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>6150</v>
+        <v>6140</v>
       </c>
       <c r="B45" t="s">
         <v>53</v>
@@ -3137,7 +3169,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>7010</v>
+        <v>6150</v>
       </c>
       <c r="B46" t="s">
         <v>54</v>
@@ -3148,7 +3180,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>7020</v>
+        <v>7010</v>
       </c>
       <c r="B47" t="s">
         <v>55</v>
@@ -3159,7 +3191,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>7110</v>
+        <v>7020</v>
       </c>
       <c r="B48" t="s">
         <v>56</v>
@@ -3170,7 +3202,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>7120</v>
+        <v>7110</v>
       </c>
       <c r="B49" t="s">
         <v>57</v>
@@ -3181,7 +3213,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>7130</v>
+        <v>7120</v>
       </c>
       <c r="B50" t="s">
         <v>58</v>
@@ -3192,10 +3224,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>8010</v>
+        <v>7130</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
@@ -3203,10 +3235,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="C52" t="s">
         <v>10</v>
@@ -3214,7 +3246,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>8110</v>
+        <v>8020</v>
       </c>
       <c r="B53" t="s">
         <v>60</v>
@@ -3225,7 +3257,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>8120</v>
+        <v>8110</v>
       </c>
       <c r="B54" t="s">
         <v>61</v>
@@ -3236,7 +3268,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>8130</v>
+        <v>8120</v>
       </c>
       <c r="B55" t="s">
         <v>62</v>
@@ -3247,7 +3279,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>9110</v>
+        <v>8130</v>
       </c>
       <c r="B56" t="s">
         <v>63</v>
@@ -3258,7 +3290,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>9120</v>
+        <v>9110</v>
       </c>
       <c r="B57" t="s">
         <v>64</v>
@@ -3269,12 +3301,23 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>9130</v>
+        <v>9120</v>
       </c>
       <c r="B58" t="s">
         <v>65</v>
       </c>
       <c r="C58" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>9130</v>
+      </c>
+      <c r="B59" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3287,7 +3330,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="15.6363636363636" customWidth="1"/>
@@ -3304,10 +3347,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3315,10 +3358,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3326,10 +3369,10 @@
         <v>1012</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3337,10 +3380,10 @@
         <v>1020</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3348,10 +3391,10 @@
         <v>1030</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3359,10 +3402,10 @@
         <v>1031</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3370,10 +3413,10 @@
         <v>1040</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3381,10 +3424,10 @@
         <v>1050</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3392,10 +3435,10 @@
         <v>1060</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3403,10 +3446,10 @@
         <v>1070</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3414,10 +3457,10 @@
         <v>1080</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3425,10 +3468,10 @@
         <v>2010</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3436,10 +3479,10 @@
         <v>3010</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3447,10 +3490,10 @@
         <v>3020</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3458,10 +3501,10 @@
         <v>7020</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3469,10 +3512,10 @@
         <v>7040</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3480,10 +3523,10 @@
         <v>7050</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3491,54 +3534,65 @@
         <v>7060</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>7080</v>
+        <v>7070</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>8010</v>
+        <v>7080</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
+        <v>8020</v>
+      </c>
+      <c r="B23" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
         <v>8030</v>
       </c>
-      <c r="B23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" t="s">
-        <v>109</v>
+      <c r="B24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -75,7 +75,7 @@
     <t>累計5回以上バトルに勝利する</t>
   </si>
   <si>
-    <t>いずれかのキャラLvを3以上にする</t>
+    <t>いずれかのキャラLvを4以上にする</t>
   </si>
   <si>
     <t>評価値を累計100以上獲得する</t>
@@ -362,10 +362,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -376,17 +376,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -399,8 +390,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -411,22 +424,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -446,15 +443,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -475,9 +474,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -491,8 +497,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -500,21 +515,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -529,7 +529,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -541,25 +619,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,67 +697,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -643,73 +709,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -723,32 +723,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -778,16 +766,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -803,20 +791,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -828,22 +828,22 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -855,118 +855,118 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1365,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>10010</v>
+        <v>15050</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1388,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>15050</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1503,7 +1503,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>14010</v>
+        <v>15050</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1543,7 +1543,7 @@
         <v>1030</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11">
         <v>-1</v>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="115">
   <si>
     <t>Id</t>
   </si>
@@ -43,6 +43,12 @@
   </si>
   <si>
     <t>Help</t>
+  </si>
+  <si>
+    <t>EnglishText</t>
+  </si>
+  <si>
+    <t>EnglishHelp</t>
   </si>
   <si>
     <t>招聘コマンドで仲間を増やす</t>
@@ -377,6 +383,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -384,7 +404,54 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -399,71 +466,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -474,8 +479,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -497,11 +503,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -514,7 +520,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -529,13 +535,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,13 +595,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,85 +673,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -667,49 +691,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -726,17 +732,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -782,26 +794,20 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -828,7 +834,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -837,136 +843,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2665,14 +2671,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C59"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
+  <dimension ref="A1:G59"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
     <col min="2" max="2" width="51.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2682,643 +2688,997 @@
       <c r="C1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1010</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1020</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1030</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1040</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1050</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1060</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1070</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2010</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2020</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2030</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2040</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2050</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2060</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2070</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2080</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>3010</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>3020</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>3030</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>3040</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>3050</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>3060</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3070</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3080</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>4010</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>4020</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>5010</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>5020</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>5030</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>5040</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>5050</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>5060</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>5110</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>5120</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>5130</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>5140</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>5150</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>6010</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>6020</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>6030</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>6040</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F41" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>6110</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C42" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>6120</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>6130</v>
       </c>
       <c r="B44" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C44" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>6140</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C45" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>6150</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>7010</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C47" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>7020</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>7110</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>7120</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>7130</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C51" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F51" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>8010</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C52" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F52" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>8020</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C53" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F53" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54">
         <v>8110</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C54" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F54" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>8120</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
+        <v>12</v>
+      </c>
+      <c r="G55" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56">
         <v>8130</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C56" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F56" t="s">
+        <v>12</v>
+      </c>
+      <c r="G56" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57">
         <v>9110</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C57" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F57" t="s">
+        <v>12</v>
+      </c>
+      <c r="G57" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58">
         <v>9120</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C58" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F58" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59">
         <v>9130</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F59" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3347,10 +3707,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3358,10 +3718,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3369,10 +3729,10 @@
         <v>1012</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3380,10 +3740,10 @@
         <v>1020</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3391,10 +3751,10 @@
         <v>1030</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3402,10 +3762,10 @@
         <v>1031</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3413,10 +3773,10 @@
         <v>1040</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3424,10 +3784,10 @@
         <v>1050</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3435,10 +3795,10 @@
         <v>1060</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3446,10 +3806,10 @@
         <v>1070</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3457,10 +3817,10 @@
         <v>1080</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3468,10 +3828,10 @@
         <v>2010</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3479,10 +3839,10 @@
         <v>3010</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3490,10 +3850,10 @@
         <v>3020</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3501,10 +3861,10 @@
         <v>7020</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3512,10 +3872,10 @@
         <v>7040</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3523,10 +3883,10 @@
         <v>7050</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3534,10 +3894,10 @@
         <v>7060</v>
       </c>
       <c r="B19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3545,10 +3905,10 @@
         <v>7070</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3556,10 +3916,10 @@
         <v>7080</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3567,10 +3927,10 @@
         <v>8010</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3578,10 +3938,10 @@
         <v>8020</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3589,10 +3949,10 @@
         <v>8030</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="172">
   <si>
     <t>Id</t>
   </si>
@@ -57,172 +57,343 @@
     <t>""</t>
   </si>
   <si>
+    <t>Recruit comrades using the recruitment command</t>
+  </si>
+  <si>
     <t>編成コマンドで仲間を編成する</t>
   </si>
   <si>
+    <t>Arrange comrades using the formation command</t>
+  </si>
+  <si>
     <t>アイテムを使用していずれかのキャラのLvを上げる</t>
   </si>
   <si>
+    <t>Level up one character by using an item</t>
+  </si>
+  <si>
     <t>献上コマンドで装備を入手する</t>
   </si>
   <si>
+    <t>Acquire equipment through the offering command</t>
+  </si>
+  <si>
     <t>取引コマンドでアイテムか装備を入手する</t>
   </si>
   <si>
+    <t>Obtain items or equipment via the trade command</t>
+  </si>
+  <si>
     <t>仲間の装備を変更する</t>
   </si>
   <si>
+    <t>Change a comrade's equipment</t>
+  </si>
+  <si>
     <t>Rank1の重要課題を全て達成する</t>
   </si>
   <si>
+    <t>Complete all Rank 1 important tasks</t>
+  </si>
+  <si>
     <t>累計1回以上出撃する</t>
   </si>
   <si>
+    <t>Sortie a total of 1 or more times</t>
+  </si>
+  <si>
     <t>累計5回以上バトルに勝利する</t>
   </si>
   <si>
+    <t>Win battles a total of 5 or more times</t>
+  </si>
+  <si>
     <t>いずれかのキャラLvを4以上にする</t>
   </si>
   <si>
+    <t>Increase one character's level to 4 or higher</t>
+  </si>
+  <si>
     <t>評価値を累計100以上獲得する</t>
   </si>
   <si>
+    <t>Accumulate an evaluation value of 100 or more</t>
+  </si>
+  <si>
     <t>与ダメージ累計が200を超える</t>
   </si>
   <si>
+    <t>Total damage dealt exceeds 200</t>
+  </si>
+  <si>
     <t>忘れられた山岳遺跡のボスを撃破する</t>
   </si>
   <si>
+    <t>Defeat the boss in the Forgotten Mountain Ruins</t>
+  </si>
+  <si>
     <t>仲間の封印魔法を2つ以上解放する</t>
   </si>
   <si>
+    <t>Unseal 2 or more sealed magic spells on comrades</t>
+  </si>
+  <si>
     <t>Rank2の重要課題を全て達成する</t>
   </si>
   <si>
+    <t>Complete all Rank 2 important tasks</t>
+  </si>
+  <si>
     <t>累計5回以上出撃する</t>
   </si>
   <si>
+    <t>Sortie a total of 5 or more times</t>
+  </si>
+  <si>
     <t>累計20回以上バトルに勝利する</t>
   </si>
   <si>
+    <t>Win battles a total of 20 or more times</t>
+  </si>
+  <si>
     <t>いずれかのキャラLvを7以上にする</t>
   </si>
   <si>
+    <t>Increase one character's level to 7 or higher</t>
+  </si>
+  <si>
     <t>評価値を累計500以上獲得する</t>
   </si>
   <si>
+    <t>Accumulate an evaluation value of 500 or more</t>
+  </si>
+  <si>
     <t>与ダメージ累計が1500を超える</t>
   </si>
   <si>
+    <t>Total damage dealt exceeds 1500</t>
+  </si>
+  <si>
     <t>月影の森のボスを撃破する</t>
   </si>
   <si>
+    <t>Defeat the boss in the Moonlit Forest</t>
+  </si>
+  <si>
     <t>仲間の封印魔法を4つ以上解放する</t>
   </si>
   <si>
+    <t>Unseal 4 or more sealed magic spells on comrades</t>
+  </si>
+  <si>
     <t>Rank3の重要課題を全て達成する</t>
   </si>
   <si>
+    <t>Complete all Rank 3 important tasks</t>
+  </si>
+  <si>
     <t>戦争(BattleField)ステージに出撃する</t>
   </si>
   <si>
+    <t>Sortie into a Battlefield stage</t>
+  </si>
+  <si>
     <t>Rank4の重要課題を全て達成する</t>
   </si>
   <si>
+    <t>Complete all Rank 4 important tasks</t>
+  </si>
+  <si>
     <t>3人以上のキャラLvを15以上にする</t>
   </si>
   <si>
+    <t>Increase the level of 3 or more characters to 15 or higher</t>
+  </si>
+  <si>
     <t>バトルで覚醒スキルを1回以上使用する</t>
   </si>
   <si>
+    <t>Use Awakening Skills at least 1 in battle</t>
+  </si>
+  <si>
     <t>バトルで交代を1回以上使用する</t>
   </si>
   <si>
+    <t>Perform a substitution at least 1 in battle</t>
+  </si>
+  <si>
     <t>亡国の宮殿跡地のボスを撃破する</t>
   </si>
   <si>
+    <t>Defeat the boss in the Ruins of the Fallen Kingdom</t>
+  </si>
+  <si>
     <t>仲間の封印魔法を6つ以上解放する</t>
   </si>
   <si>
+    <t>Unseal 6 or more sealed magic spells on comrades</t>
+  </si>
+  <si>
     <t>Rank5の重要課題を全て達成する</t>
   </si>
   <si>
+    <t>Complete all Rank 5 important tasks</t>
+  </si>
+  <si>
     <t>累計10回以上出撃する</t>
   </si>
   <si>
+    <t>Sortie a total of 10 or more times</t>
+  </si>
+  <si>
     <t>累計50回以上バトルに勝利する</t>
   </si>
   <si>
+    <t>Win battles a total of 50 or more times</t>
+  </si>
+  <si>
     <t>いずれかのキャラLvを15以上にする</t>
   </si>
   <si>
+    <t>Increase one character's level to 15 or higher</t>
+  </si>
+  <si>
     <t>評価値を累計1500以上獲得する</t>
   </si>
   <si>
+    <t>Accumulate an evaluation value of 1500 or more</t>
+  </si>
+  <si>
     <t>与ダメージ累計が5000を超える</t>
   </si>
   <si>
+    <t>Total damage dealt exceeds 5000</t>
+  </si>
+  <si>
     <t>いずれかのキャラをクラスチェンジする</t>
   </si>
   <si>
+    <t>Change the class of one character</t>
+  </si>
+  <si>
     <t>暗黒の塔のボスを撃破する</t>
   </si>
   <si>
+    <t>Defeat the boss in the Dark Tower</t>
+  </si>
+  <si>
     <t>仲間の封印魔法を8つ以上解放する</t>
   </si>
   <si>
+    <t>Unseal 8 or more sealed magic spells on comrades</t>
+  </si>
+  <si>
     <t>Rank7の重要課題を全て達成する</t>
   </si>
   <si>
+    <t>Complete all Rank 7 important tasks</t>
+  </si>
+  <si>
     <t>累計15回以上出撃する</t>
   </si>
   <si>
+    <t>Sortie a total of 15 or more times</t>
+  </si>
+  <si>
     <t>累計75回以上バトルに勝利する</t>
   </si>
   <si>
+    <t>Win battles a total of 75 or more times</t>
+  </si>
+  <si>
     <t>いずれかのキャラLvを20以上にする</t>
   </si>
   <si>
+    <t>Increase one character's level to 20 or higher</t>
+  </si>
+  <si>
     <t>評価値を累計3000以上獲得する</t>
   </si>
   <si>
+    <t>Accumulate an evaluation value of 3000 or more</t>
+  </si>
+  <si>
     <t>与ダメージ累計が7500を超える</t>
   </si>
   <si>
+    <t>Total damage dealt exceeds 7500</t>
+  </si>
+  <si>
     <t>天空城のボスを撃破する</t>
   </si>
   <si>
+    <t>Defeat the boss in Sky City</t>
+  </si>
+  <si>
     <t>Rank8の重要課題を全て達成する</t>
   </si>
   <si>
+    <t>Complete all Rank 8 important tasks</t>
+  </si>
+  <si>
     <t>3人以上のキャラLvを25以上にする</t>
   </si>
   <si>
+    <t>Increase the level of 3 or more characters to 25 or higher</t>
+  </si>
+  <si>
     <t>バトルで覚醒スキルを5回以上使用する</t>
   </si>
   <si>
+    <t>Use Awakening Skills at least 5 in battle</t>
+  </si>
+  <si>
     <t>バトルで交代を5回以上使用する</t>
   </si>
   <si>
+    <t>Perform a substitution at least 5 in battle</t>
+  </si>
+  <si>
     <t>Rank9の重要課題を全て達成する</t>
   </si>
   <si>
+    <t>Complete all Rank 9 important tasks</t>
+  </si>
+  <si>
     <t>5人以上のキャラLvを25以上にする</t>
   </si>
   <si>
+    <t>Increase the level of 5 or more characters to 25 or higher</t>
+  </si>
+  <si>
     <t>エインフェリアを2人転送する</t>
   </si>
   <si>
+    <t>Transfer 2 Enferia</t>
+  </si>
+  <si>
     <t>3人以上のキャラをクラスチェンジする</t>
   </si>
   <si>
+    <t>Change the class of 3 or more characters</t>
+  </si>
+  <si>
     <t>5人以上のキャラLvを30以上にする</t>
   </si>
   <si>
+    <t>Increase the level of 5 or more characters to 30 or higher</t>
+  </si>
+  <si>
     <t>エインフェリアを3人転送する</t>
   </si>
   <si>
+    <t>Transfer 3 Enferia</t>
+  </si>
+  <si>
     <t>5人以上のキャラをクラスチェンジする</t>
+  </si>
+  <si>
+    <t>Change the class of 5 or more characters</t>
   </si>
   <si>
     <t>Complete</t>
@@ -368,10 +539,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -383,59 +554,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -446,14 +565,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -473,7 +584,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -481,13 +622,19 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -511,6 +658,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -519,8 +681,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -535,13 +706,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,49 +760,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -613,37 +778,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,7 +802,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -667,19 +832,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,7 +850,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -709,13 +874,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -726,30 +897,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -772,7 +919,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -795,19 +957,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -826,6 +977,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -834,145 +1005,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2676,6 +2847,8 @@
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
     <col min="2" max="2" width="51.4545454545455" customWidth="1"/>
+    <col min="6" max="6" width="46.9363636363636" customWidth="1"/>
+    <col min="7" max="7" width="42.9727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2706,7 +2879,7 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -2717,13 +2890,13 @@
         <v>1020</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -2734,13 +2907,13 @@
         <v>1030</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
         <v>12</v>
@@ -2751,13 +2924,13 @@
         <v>1040</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
@@ -2768,13 +2941,13 @@
         <v>1050</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
@@ -2785,13 +2958,13 @@
         <v>1060</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -2802,13 +2975,13 @@
         <v>1070</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
@@ -2819,13 +2992,13 @@
         <v>2010</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
         <v>12</v>
@@ -2836,13 +3009,13 @@
         <v>2020</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
         <v>12</v>
@@ -2853,13 +3026,13 @@
         <v>2030</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G11" t="s">
         <v>12</v>
@@ -2870,13 +3043,13 @@
         <v>2040</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G12" t="s">
         <v>12</v>
@@ -2887,13 +3060,13 @@
         <v>2050</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G13" t="s">
         <v>12</v>
@@ -2904,13 +3077,13 @@
         <v>2060</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -2921,13 +3094,13 @@
         <v>2070</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
         <v>12</v>
@@ -2938,13 +3111,13 @@
         <v>2080</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="G16" t="s">
         <v>12</v>
@@ -2955,13 +3128,13 @@
         <v>3010</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="G17" t="s">
         <v>12</v>
@@ -2972,13 +3145,13 @@
         <v>3020</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
         <v>12</v>
@@ -2989,13 +3162,13 @@
         <v>3030</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="G19" t="s">
         <v>12</v>
@@ -3006,13 +3179,13 @@
         <v>3040</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="G20" t="s">
         <v>12</v>
@@ -3023,13 +3196,13 @@
         <v>3050</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>
@@ -3040,13 +3213,13 @@
         <v>3060</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="G22" t="s">
         <v>12</v>
@@ -3057,13 +3230,13 @@
         <v>3070</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="G23" t="s">
         <v>12</v>
@@ -3074,13 +3247,13 @@
         <v>3080</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
         <v>12</v>
@@ -3091,13 +3264,13 @@
         <v>4010</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="G25" t="s">
         <v>12</v>
@@ -3108,13 +3281,13 @@
         <v>4020</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="G26" t="s">
         <v>12</v>
@@ -3125,13 +3298,13 @@
         <v>5010</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="G27" t="s">
         <v>12</v>
@@ -3142,13 +3315,13 @@
         <v>5020</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="G28" t="s">
         <v>12</v>
@@ -3159,13 +3332,13 @@
         <v>5030</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="G29" t="s">
         <v>12</v>
@@ -3176,13 +3349,13 @@
         <v>5040</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G30" t="s">
         <v>12</v>
@@ -3193,13 +3366,13 @@
         <v>5050</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="G31" t="s">
         <v>12</v>
@@ -3210,13 +3383,13 @@
         <v>5060</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="G32" t="s">
         <v>12</v>
@@ -3227,13 +3400,13 @@
         <v>5110</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="G33" t="s">
         <v>12</v>
@@ -3244,13 +3417,13 @@
         <v>5120</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s">
         <v>12</v>
@@ -3261,13 +3434,13 @@
         <v>5130</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s">
         <v>12</v>
@@ -3278,13 +3451,13 @@
         <v>5140</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="C36" t="s">
         <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s">
         <v>12</v>
@@ -3295,13 +3468,13 @@
         <v>5150</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="G37" t="s">
         <v>12</v>
@@ -3312,13 +3485,13 @@
         <v>6010</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="G38" t="s">
         <v>12</v>
@@ -3329,13 +3502,13 @@
         <v>6020</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
       </c>
       <c r="F39" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="G39" t="s">
         <v>12</v>
@@ -3346,13 +3519,13 @@
         <v>6030</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
       </c>
       <c r="F40" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="G40" t="s">
         <v>12</v>
@@ -3363,13 +3536,13 @@
         <v>6040</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
       </c>
       <c r="F41" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="G41" t="s">
         <v>12</v>
@@ -3380,13 +3553,13 @@
         <v>6110</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
       </c>
       <c r="F42" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s">
         <v>12</v>
@@ -3397,13 +3570,13 @@
         <v>6120</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
       </c>
       <c r="F43" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="G43" t="s">
         <v>12</v>
@@ -3414,13 +3587,13 @@
         <v>6130</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
       </c>
       <c r="F44" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="G44" t="s">
         <v>12</v>
@@ -3431,13 +3604,13 @@
         <v>6140</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
       </c>
       <c r="F45" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="G45" t="s">
         <v>12</v>
@@ -3448,13 +3621,13 @@
         <v>6150</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
       </c>
       <c r="F46" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="G46" t="s">
         <v>12</v>
@@ -3465,13 +3638,13 @@
         <v>7010</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="C47" t="s">
         <v>12</v>
       </c>
       <c r="F47" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="G47" t="s">
         <v>12</v>
@@ -3482,13 +3655,13 @@
         <v>7020</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="C48" t="s">
         <v>12</v>
       </c>
       <c r="F48" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="G48" t="s">
         <v>12</v>
@@ -3499,13 +3672,13 @@
         <v>7110</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="C49" t="s">
         <v>12</v>
       </c>
       <c r="F49" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="G49" t="s">
         <v>12</v>
@@ -3516,13 +3689,13 @@
         <v>7120</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="C50" t="s">
         <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="G50" t="s">
         <v>12</v>
@@ -3533,13 +3706,13 @@
         <v>7130</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="C51" t="s">
         <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="G51" t="s">
         <v>12</v>
@@ -3550,13 +3723,13 @@
         <v>8010</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C52" t="s">
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="G52" t="s">
         <v>12</v>
@@ -3567,13 +3740,13 @@
         <v>8020</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="G53" t="s">
         <v>12</v>
@@ -3584,13 +3757,13 @@
         <v>8110</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="G54" t="s">
         <v>12</v>
@@ -3601,13 +3774,13 @@
         <v>8120</v>
       </c>
       <c r="B55" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="C55" t="s">
         <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="G55" t="s">
         <v>12</v>
@@ -3618,13 +3791,13 @@
         <v>8130</v>
       </c>
       <c r="B56" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="C56" t="s">
         <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>12</v>
+        <v>119</v>
       </c>
       <c r="G56" t="s">
         <v>12</v>
@@ -3635,13 +3808,13 @@
         <v>9110</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="G57" t="s">
         <v>12</v>
@@ -3652,13 +3825,13 @@
         <v>9120</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="C58" t="s">
         <v>12</v>
       </c>
       <c r="F58" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="G58" t="s">
         <v>12</v>
@@ -3669,13 +3842,13 @@
         <v>9130</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="C59" t="s">
         <v>12</v>
       </c>
       <c r="F59" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="G59" t="s">
         <v>12</v>
@@ -3707,10 +3880,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3718,10 +3891,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3729,10 +3902,10 @@
         <v>1012</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3740,10 +3913,10 @@
         <v>1020</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3751,10 +3924,10 @@
         <v>1030</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3762,10 +3935,10 @@
         <v>1031</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3773,10 +3946,10 @@
         <v>1040</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3784,10 +3957,10 @@
         <v>1050</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3795,10 +3968,10 @@
         <v>1060</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3806,10 +3979,10 @@
         <v>1070</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3817,10 +3990,10 @@
         <v>1080</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3828,10 +4001,10 @@
         <v>2010</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3839,10 +4012,10 @@
         <v>3010</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3850,10 +4023,10 @@
         <v>3020</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3861,10 +4034,10 @@
         <v>7020</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>154</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3872,10 +4045,10 @@
         <v>7040</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3883,10 +4056,10 @@
         <v>7050</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3894,10 +4067,10 @@
         <v>7060</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>160</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3905,10 +4078,10 @@
         <v>7070</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3916,10 +4089,10 @@
         <v>7080</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3927,10 +4100,10 @@
         <v>8010</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>166</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3938,10 +4111,10 @@
         <v>8020</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>168</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3949,10 +4122,10 @@
         <v>8030</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="174">
   <si>
     <t>Id</t>
   </si>
@@ -532,6 +532,12 @@
   </si>
   <si>
     <t>メンバーの戦力値</t>
+  </si>
+  <si>
+    <t>EvaluateValue</t>
+  </si>
+  <si>
+    <t>ピリオド評価値</t>
   </si>
 </sst>
 </file>
@@ -541,8 +547,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -550,6 +556,21 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -561,7 +582,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -569,44 +598,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -621,8 +614,45 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -636,7 +666,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -650,14 +688,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -667,31 +697,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -712,7 +718,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -724,13 +736,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -748,7 +760,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -760,13 +772,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -778,7 +790,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -790,43 +802,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -844,13 +820,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -862,13 +850,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -880,13 +880,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -897,6 +903,24 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -911,6 +935,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -939,6 +978,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -953,50 +1003,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1005,145 +1011,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3863,7 +3869,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"